--- a/reports/ASX_Strong_Buy_Screener_2026-09-01.xlsx
+++ b/reports/ASX_Strong_Buy_Screener_2026-09-01.xlsx
@@ -573,7 +573,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Report generated: 2026-09-01 00:01 </t>
+          <t xml:space="preserve">Report generated: 2026-09-01 22:44 </t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="C2" s="6" t="n">
-        <v>6.61</v>
+        <v>6.63</v>
       </c>
       <c r="D2" s="6" t="n">
         <v>9.970000000000001</v>
@@ -926,13 +926,13 @@
         <v>4.88</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>0.0401</v>
+        <v>0.0388</v>
       </c>
       <c r="G2" s="7" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="H2" s="7" t="n">
-        <v>0.1604</v>
+        <v>0.1553</v>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
@@ -940,13 +940,13 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>27.54</v>
+        <v>27.63</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>5.36</v>
+        <v>5.38</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="M2" s="5" t="n">
         <v>2.27</v>
@@ -968,7 +968,7 @@
       </c>
       <c r="Q2" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>8.58</v>
+        <v>8.68</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>10.63</v>
@@ -1143,13 +1143,13 @@
         <v>7.94</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0.0387</v>
+        <v>0.0353</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0707</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>0.1546</v>
+        <v>0.1413</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>7.66</v>
+        <v>7.75</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="M5" s="9" t="n">
         <v>0.77</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
         </is>
       </c>
       <c r="C6" s="10" t="n">
-        <v>7.23</v>
+        <v>7.09</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>7.75</v>
@@ -1210,13 +1210,13 @@
         <v>6.54</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>0.004</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>0.008</v>
+        <v>0.0173</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>0.016</v>
+        <v>0.0347</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>45.19</v>
+        <v>44.31</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>12.35</v>
+        <v>12.11</v>
       </c>
       <c r="M6" s="9" t="n">
         <v>0.26</v>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -1268,22 +1268,22 @@
         </is>
       </c>
       <c r="C7" s="10" t="n">
-        <v>43.06</v>
+        <v>43.8</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>43.31</v>
+        <v>43.9</v>
       </c>
       <c r="E7" s="10" t="n">
         <v>27.575</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>-0.0016</v>
+        <v>-0.0058</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>-0.0033</v>
+        <v>-0.0117</v>
       </c>
       <c r="H7" s="11" t="n">
-        <v>-0.0066</v>
+        <v>-0.0233</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
@@ -1291,13 +1291,13 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>7.01</v>
+        <v>7.11</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="M7" s="9" t="n">
         <v>1.15</v>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -1335,22 +1335,22 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>60.92</v>
+        <v>60.51</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>72.95</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>44.18</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>0.0224</v>
+        <v>0.0243</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0.0449</v>
+        <v>0.0486</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.0897</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
@@ -1358,13 +1358,13 @@
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>25.6</v>
+        <v>25.53</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>5.95</v>
+        <v>5.91</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>5.78</v>
+        <v>5.74</v>
       </c>
       <c r="M8" s="5" t="n">
         <v>0.31</v>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="Q8" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>22.23</v>
+        <v>22.07</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>26.17</v>
@@ -1411,13 +1411,13 @@
         <v>18.025</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>0.0258</v>
+        <v>0.0278</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>0.0516</v>
+        <v>0.0556</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.1032</v>
+        <v>0.1111</v>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
@@ -1425,13 +1425,13 @@
         </is>
       </c>
       <c r="J9" s="5" t="n">
-        <v>35.29</v>
+        <v>35.03</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>6.64</v>
+        <v>6.59</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>3.4</v>
+        <v>3.37</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>0.92</v>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="Q9" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0.6</v>
+        <v>0.635</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>0.95</v>
@@ -1478,13 +1478,13 @@
         <v>0.6</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0.6458</v>
+        <v>0.5965</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1.2917</v>
+        <v>1.1929</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>2.5833</v>
+        <v>2.3858</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="J10" s="5" t="n">
-        <v>-18.01</v>
+        <v>-19.06</v>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="Q10" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>4.59</v>
+        <v>4.54</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>5.4</v>
@@ -1551,13 +1551,13 @@
         <v>4.2</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>0.0102</v>
+        <v>0.013</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>0.0204</v>
+        <v>0.0261</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>0.0407</v>
+        <v>0.0522</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
@@ -1565,13 +1565,13 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>57.38</v>
+        <v>56.75</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>42.55</v>
+        <v>42.08</v>
       </c>
       <c r="M11" s="9" t="n">
         <v>0.31</v>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="Q11" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>64.78</v>
+        <v>64.72</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>71.09999999999999</v>
@@ -1618,13 +1618,13 @@
         <v>51.2</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.0199</v>
+        <v>0.0229</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.0399</v>
+        <v>0.0459</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.0917</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>19.57</v>
+        <v>19.44</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>1.82</v>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -1676,22 +1676,22 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="E13" s="10" t="n">
         <v>1.14</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>-0.0012</v>
+        <v>-0.0092</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>-0.0023</v>
+        <v>-0.0185</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>-0.0046</v>
+        <v>-0.037</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
@@ -1699,10 +1699,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>34</v>
+        <v>35.14</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="L13" s="9" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="Q13" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>40.77</v>
+        <v>41.39</v>
       </c>
       <c r="D14" s="10" t="n">
         <v>42.54</v>
@@ -1754,13 +1754,13 @@
         <v>25.05</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>-0.012</v>
+        <v>-0.0147</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>-0.0239</v>
+        <v>-0.0295</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>-0.0479</v>
+        <v>-0.0589</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
@@ -1768,13 +1768,13 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>20.08</v>
+        <v>20.49</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="M14" s="9" t="n">
         <v>0.37</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="Q14" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>37.2</v>
+        <v>37.34</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>41</v>
@@ -1821,13 +1821,13 @@
         <v>32.46</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>-0.0051</v>
+        <v>-0.0061</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>-0.0103</v>
+        <v>-0.0121</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>-0.0206</v>
+        <v>-0.0243</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>18.88</v>
+        <v>18.95</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>1.58</v>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="Q15" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>10.89</v>
+        <v>10.83</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>11.1</v>
@@ -1892,13 +1892,13 @@
         <v>8.445</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>-0.0258</v>
+        <v>-0.0246</v>
       </c>
       <c r="G16" s="11" t="n">
-        <v>-0.0516</v>
+        <v>-0.0491</v>
       </c>
       <c r="H16" s="11" t="n">
-        <v>-0.1032</v>
+        <v>-0.0983</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>68.06</v>
+        <v>67.69</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>5.34</v>
+        <v>5.31</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>4.8</v>
+        <v>4.77</v>
       </c>
       <c r="M16" s="9" t="n">
         <v>5.26</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="Q16" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>21.36</v>
+        <v>21.32</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>35.64</v>
@@ -1959,13 +1959,13 @@
         <v>19.47</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>0.053</v>
+        <v>0.0527</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.106</v>
+        <v>0.1054</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0.2119</v>
+        <v>0.2109</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
@@ -1973,10 +1973,10 @@
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>25.13</v>
+        <v>25.08</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="L17" s="5" t="n">
         <v>0.41</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="Q18" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="C19" s="10" t="n">
-        <v>19.24</v>
+        <v>19.25</v>
       </c>
       <c r="D19" s="10" t="n">
         <v>40.7</v>
@@ -2101,13 +2101,13 @@
         <v>16.93</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>0.0565</v>
+        <v>0.0563</v>
       </c>
       <c r="G19" s="11" t="n">
-        <v>0.113</v>
+        <v>0.1127</v>
       </c>
       <c r="H19" s="11" t="n">
-        <v>0.2259</v>
+        <v>0.2253</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>17.33</v>
+        <v>17.34</v>
       </c>
       <c r="K19" s="9" t="n">
         <v>2.17</v>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="Q19" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -2159,22 +2159,22 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="E20" s="10" t="n">
         <v>2.2</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.0822</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.1644</v>
+        <v>0.176</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.3288</v>
+        <v>0.3521</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -2182,13 +2182,13 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>7.03</v>
+        <v>6.91</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>8.050000000000001</v>
+        <v>7.91</v>
       </c>
       <c r="M20" s="9" t="n">
         <v>0.35</v>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="Q20" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>56.14</v>
+        <v>55.61</v>
       </c>
       <c r="D21" s="10" t="n">
         <v>62.9</v>
@@ -2235,13 +2235,13 @@
         <v>44.3</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.0138</v>
+        <v>0.0163</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.0276</v>
+        <v>0.0327</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.0553</v>
+        <v>0.0653</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>22.55</v>
+        <v>22.33</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>8.69</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M21" s="9" t="n">
         <v>0.12</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="Q21" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>29.17</v>
+        <v>28.57</v>
       </c>
       <c r="D22" s="6" t="n">
         <v>40.28</v>
@@ -2302,13 +2302,13 @@
         <v>22.08</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0521</v>
+        <v>0.0585</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.1042</v>
+        <v>0.1169</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.2085</v>
+        <v>0.2338</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
@@ -2316,13 +2316,13 @@
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>37.4</v>
+        <v>36.63</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="M22" s="5" t="n">
         <v>0.55</v>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="Q23" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>3.66</v>
+        <v>3.69</v>
       </c>
       <c r="D24" s="10" t="n">
         <v>4.42</v>
@@ -2444,13 +2444,13 @@
         <v>3.14</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>0.0052</v>
+        <v>0.0031</v>
       </c>
       <c r="G24" s="11" t="n">
-        <v>0.0103</v>
+        <v>0.0062</v>
       </c>
       <c r="H24" s="11" t="n">
-        <v>0.0206</v>
+        <v>0.0123</v>
       </c>
       <c r="I24" s="9" t="inlineStr">
         <is>
@@ -2458,13 +2458,13 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>17.43</v>
+        <v>17.57</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M24" s="9" t="n">
         <v>1.48</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="Q24" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -2502,22 +2502,22 @@
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>0.68</v>
+        <v>0.78</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>3.97</v>
+        <v>3.69</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>0.355</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0249</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.0164</v>
+        <v>-0.0498</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>0.0328</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
@@ -2525,13 +2525,13 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>15.26</v>
+        <v>17.51</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="M25" s="9" t="n">
         <v>0.76</v>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="Q25" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -2569,22 +2569,22 @@
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>10.73</v>
+        <v>10.48</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>13.37</v>
+        <v>13.32</v>
       </c>
       <c r="E26" s="10" t="n">
         <v>9.81</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>-0.0072</v>
+        <v>-0.0014</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>-0.0144</v>
+        <v>-0.0029</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>-0.0289</v>
+        <v>-0.0057</v>
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
@@ -2592,13 +2592,13 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>17.03</v>
+        <v>16.63</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="M26" s="9" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="Q26" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>6.06</v>
+        <v>6.11</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>6.89</v>
@@ -2647,13 +2647,13 @@
         <v>4.93</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>0.039</v>
+        <v>0.0366</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>0.078</v>
+        <v>0.0733</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>0.156</v>
+        <v>0.1466</v>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="J27" s="5" t="n">
-        <v>33.67</v>
+        <v>33.94</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="L27" s="5" t="n">
         <v>0.49</v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -2705,7 +2705,7 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>66.23</v>
+        <v>66.84</v>
       </c>
       <c r="D28" s="10" t="n">
         <v>68.77</v>
@@ -2714,13 +2714,13 @@
         <v>39.3</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>-0.0219</v>
+        <v>-0.0286</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>-0.0437</v>
+        <v>-0.0572</v>
       </c>
       <c r="H28" s="11" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.1145</v>
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
@@ -2728,13 +2728,13 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>24.62</v>
+        <v>24.76</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>4.74</v>
+        <v>4.77</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>5.73</v>
+        <v>5.78</v>
       </c>
       <c r="M28" s="9" t="n">
         <v>0.5</v>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="Q28" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="Q29" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="Q30" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:44</t>
         </is>
       </c>
     </row>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="Q31" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>6.53</v>
+        <v>6.56</v>
       </c>
       <c r="D32" s="10" t="n">
         <v>7.48</v>
@@ -3006,13 +3006,13 @@
         <v>5.91</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.0101</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>-0.0181</v>
+        <v>-0.0203</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>-0.0361</v>
+        <v>-0.0405</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
@@ -3020,13 +3020,13 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>43.53</v>
+        <v>43.73</v>
       </c>
       <c r="K32" s="9" t="n">
         <v>0.73</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="M32" s="9" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="Q32" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="C33" s="10" t="n">
-        <v>0.865</v>
+        <v>0.895</v>
       </c>
       <c r="D33" s="10" t="n">
         <v>1.335</v>
@@ -3075,13 +3075,13 @@
         <v>0.8149999999999999</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>0.0431</v>
+        <v>0.0333</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.0862</v>
+        <v>0.0665</v>
       </c>
       <c r="H33" s="11" t="n">
-        <v>0.1723</v>
+        <v>0.133</v>
       </c>
       <c r="I33" s="9" t="inlineStr">
         <is>
@@ -3089,10 +3089,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>7.21</v>
+        <v>7.46</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="L33" s="9" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="Q33" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>32.42</v>
+        <v>33.05</v>
       </c>
       <c r="D34" s="6" t="n">
         <v>35.48</v>
@@ -3144,13 +3144,13 @@
         <v>25.41</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0.0266</v>
+        <v>0.0213</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>0.0532</v>
+        <v>0.0426</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>0.1063</v>
+        <v>0.0852</v>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="J34" s="5" t="n">
-        <v>34.49</v>
+        <v>35.16</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>4.44</v>
+        <v>4.52</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>2.59</v>
+        <v>2.64</v>
       </c>
       <c r="M34" s="5" t="n">
         <v>0.14</v>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="C35" s="10" t="n">
-        <v>31.07</v>
+        <v>31.35</v>
       </c>
       <c r="D35" s="10" t="n">
         <v>35.26</v>
@@ -3211,13 +3211,13 @@
         <v>20.23</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>0.0328</v>
+        <v>0.0302</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.0655</v>
+        <v>0.0605</v>
       </c>
       <c r="H35" s="11" t="n">
-        <v>0.1311</v>
+        <v>0.121</v>
       </c>
       <c r="I35" s="9" t="inlineStr">
         <is>
@@ -3225,10 +3225,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>17.17</v>
+        <v>17.32</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="L35" s="9" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="Q35" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="D36" s="10" t="n">
         <v>4.12</v>
@@ -3280,13 +3280,13 @@
         <v>3.51</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>0.0105</v>
+        <v>0.0119</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>0.021</v>
+        <v>0.0238</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>0.0419</v>
+        <v>0.0477</v>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
@@ -3294,13 +3294,13 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>6.55</v>
+        <v>6.52</v>
       </c>
       <c r="K36" s="9" t="n">
         <v>0.86</v>
       </c>
       <c r="L36" s="9" t="n">
-        <v>13.77</v>
+        <v>13.7</v>
       </c>
       <c r="M36" s="9" t="n">
         <v>0.23</v>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="Q36" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="C37" s="10" t="n">
-        <v>19.59</v>
+        <v>19.44</v>
       </c>
       <c r="D37" s="10" t="n">
         <v>26.93</v>
@@ -3347,13 +3347,13 @@
         <v>16.18</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>0.0228</v>
+        <v>0.0259</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>0.0456</v>
+        <v>0.0518</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>0.0911</v>
+        <v>0.1036</v>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>20.2</v>
+        <v>20.04</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>5.82</v>
+        <v>5.76</v>
       </c>
       <c r="L37" s="9" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="M37" s="9" t="n">
         <v>0.9399999999999999</v>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="Q37" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -3405,22 +3405,22 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>27.65</v>
+        <v>26.5</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>40.57</v>
+        <v>40.24</v>
       </c>
       <c r="E38" s="6" t="n">
         <v>21.47</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>0.0513</v>
+        <v>0.0643</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>0.1025</v>
+        <v>0.1287</v>
       </c>
       <c r="H38" s="7" t="n">
-        <v>0.2051</v>
+        <v>0.2574</v>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
@@ -3428,13 +3428,13 @@
         </is>
       </c>
       <c r="J38" s="5" t="n">
-        <v>33.31</v>
+        <v>31.93</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>3.82</v>
+        <v>3.66</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>8.359999999999999</v>
+        <v>8.01</v>
       </c>
       <c r="M38" s="5" t="n">
         <v>0.57</v>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="Q38" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
         </is>
       </c>
       <c r="C39" s="10" t="n">
-        <v>159.9</v>
+        <v>159.15</v>
       </c>
       <c r="D39" s="10" t="n">
         <v>185.59</v>
@@ -3481,13 +3481,13 @@
         <v>146.98</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>-0.0542</v>
+        <v>-0.0533</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>-0.1085</v>
+        <v>-0.1066</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>-0.2169</v>
+        <v>-0.2132</v>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
@@ -3495,13 +3495,13 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>24.56</v>
+        <v>24.45</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="L39" s="9" t="n">
-        <v>9.1</v>
+        <v>9.06</v>
       </c>
       <c r="M39" s="9" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="Q39" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="C40" s="6" t="n">
-        <v>14.01</v>
+        <v>14.25</v>
       </c>
       <c r="D40" s="6" t="n">
         <v>17.16</v>
@@ -3550,13 +3550,13 @@
         <v>9.5</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>0.055</v>
+        <v>0.0499</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>0.11</v>
+        <v>0.0997</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>0.22</v>
+        <v>0.1995</v>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
@@ -3564,13 +3564,13 @@
         </is>
       </c>
       <c r="J40" s="5" t="n">
-        <v>9.039999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="M40" s="5" t="n">
         <v>0.54</v>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="Q40" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="Q41" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>9.449999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="D42" s="10" t="n">
         <v>10.85</v>
@@ -3692,13 +3692,13 @@
         <v>7.25</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>0.0278</v>
+        <v>0.0263</v>
       </c>
       <c r="G42" s="11" t="n">
-        <v>0.0556</v>
+        <v>0.0526</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>0.1111</v>
+        <v>0.1053</v>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
@@ -3706,13 +3706,13 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>16.58</v>
+        <v>16.67</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="L42" s="9" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="M42" s="9" t="n">
         <v>2.08</v>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="Q42" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>19.32</v>
+        <v>19.11</v>
       </c>
       <c r="D43" s="10" t="n">
         <v>25.95</v>
@@ -3759,13 +3759,13 @@
         <v>18.18</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.0594</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="G43" s="11" t="n">
-        <v>0.1188</v>
+        <v>0.1256</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>0.2377</v>
+        <v>0.2513</v>
       </c>
       <c r="I43" s="9" t="inlineStr">
         <is>
@@ -3773,13 +3773,13 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>21.71</v>
+        <v>21.47</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="L43" s="9" t="n">
-        <v>11.26</v>
+        <v>11.14</v>
       </c>
       <c r="M43" s="9" t="n">
         <v>0.26</v>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="Q43" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>3.51</v>
+        <v>3.54</v>
       </c>
       <c r="D44" s="10" t="n">
         <v>6.685</v>
@@ -3826,13 +3826,13 @@
         <v>3.215</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>0.0861</v>
+        <v>0.0833</v>
       </c>
       <c r="G44" s="11" t="n">
-        <v>0.1722</v>
+        <v>0.1667</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>0.3445</v>
+        <v>0.3333</v>
       </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
@@ -3840,13 +3840,13 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>17.55</v>
+        <v>17.7</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="L44" s="9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="M44" s="9" t="n">
         <v>0.88</v>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="Q44" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="C45" s="10" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="D45" s="10" t="n">
         <v>3.59</v>
@@ -3893,13 +3893,13 @@
         <v>2.83</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>0.0402</v>
+        <v>0.0412</v>
       </c>
       <c r="G45" s="11" t="n">
-        <v>0.0805</v>
+        <v>0.0825</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>0.1609</v>
+        <v>0.1649</v>
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
@@ -3907,13 +3907,13 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>11.23</v>
+        <v>11.19</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="L45" s="9" t="n">
-        <v>7.11</v>
+        <v>7.08</v>
       </c>
       <c r="M45" s="9" t="n">
         <v>0.5600000000000001</v>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="Q45" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>8.15</v>
+        <v>8.33</v>
       </c>
       <c r="D46" s="10" t="n">
         <v>12.73</v>
@@ -3960,13 +3960,13 @@
         <v>7.64</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>0.065</v>
+        <v>0.0582</v>
       </c>
       <c r="G46" s="11" t="n">
-        <v>0.13</v>
+        <v>0.1164</v>
       </c>
       <c r="H46" s="11" t="n">
-        <v>0.2599</v>
+        <v>0.2327</v>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>20.9</v>
+        <v>21.36</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="L46" s="9" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="M46" s="9" t="n">
         <v>2</v>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="Q46" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="C47" s="10" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="D47" s="10" t="n">
         <v>4.66</v>
@@ -4027,13 +4027,13 @@
         <v>3.3</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>0.0255</v>
+        <v>0.0263</v>
       </c>
       <c r="G47" s="11" t="n">
-        <v>0.051</v>
+        <v>0.0526</v>
       </c>
       <c r="H47" s="11" t="n">
-        <v>0.102</v>
+        <v>0.1052</v>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
@@ -4041,13 +4041,13 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>8.970000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="K47" s="9" t="n">
         <v>0.74</v>
       </c>
       <c r="L47" s="9" t="n">
-        <v>13.01</v>
+        <v>12.97</v>
       </c>
       <c r="M47" s="9" t="n">
         <v>0.45</v>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="Q47" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="C48" s="6" t="n">
-        <v>0.38</v>
+        <v>0.375</v>
       </c>
       <c r="D48" s="6" t="n">
         <v>0.5</v>
@@ -4094,13 +4094,13 @@
         <v>0.375</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.1118</v>
+        <v>0.1167</v>
       </c>
       <c r="G48" s="7" t="n">
-        <v>0.2237</v>
+        <v>0.2333</v>
       </c>
       <c r="H48" s="7" t="n">
-        <v>0.4474</v>
+        <v>0.4667</v>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
@@ -4108,13 +4108,13 @@
         </is>
       </c>
       <c r="J48" s="5" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>4.98</v>
+        <v>4.91</v>
       </c>
       <c r="M48" s="5" t="n">
         <v>0.51</v>
@@ -4131,12 +4131,12 @@
       </c>
       <c r="P48" s="8" t="inlineStr">
         <is>
-          <t>Cromwell Property Group is a real estate investor and manager with $5.0 billion of assets under management in Australia and New Zealand on 31 December 2025. Cromwell is a trusted partner to a broad range of local and global investors, capital providers and banking partners, with a strong track record of creating value and delivering risk-adjusted returns throughout the real estate investment cy...</t>
+          <t>Cromwell Property Group is a real estate investor and manager with 4.7 billion dollars of assets under management in Australia and New Zealand at 30 June 2026. Cromwell is a trusted partner to a broad range of local and global investors, capital providers and banking partners, with a strong track record of creating value and delivering risk-adjusted returns throughout the real estate investment...</t>
         </is>
       </c>
       <c r="Q48" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -4152,22 +4152,22 @@
         </is>
       </c>
       <c r="C49" s="6" t="n">
-        <v>7.31</v>
+        <v>7.24</v>
       </c>
       <c r="D49" s="6" t="n">
         <v>8.960000000000001</v>
       </c>
       <c r="E49" s="6" t="n">
-        <v>7.28</v>
+        <v>7.17</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0386</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>0.0726</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="H49" s="7" t="n">
-        <v>0.1452</v>
+        <v>0.1546</v>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
@@ -4175,13 +4175,13 @@
         </is>
       </c>
       <c r="J49" s="5" t="n">
-        <v>104.43</v>
+        <v>103.43</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="M49" s="5" t="n">
         <v>4.01</v>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:01</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="C50" s="10" t="n">
-        <v>133.92</v>
+        <v>134.35</v>
       </c>
       <c r="D50" s="10" t="n">
         <v>303.74</v>
@@ -4228,13 +4228,13 @@
         <v>88.73999999999999</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>0.0114</v>
+        <v>0.0106</v>
       </c>
       <c r="G50" s="11" t="n">
-        <v>0.0228</v>
+        <v>0.0212</v>
       </c>
       <c r="H50" s="11" t="n">
-        <v>0.0457</v>
+        <v>0.0423</v>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
@@ -4242,13 +4242,13 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>59.52</v>
+        <v>59.45</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>5.03</v>
+        <v>5.05</v>
       </c>
       <c r="L50" s="9" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="M50" s="9" t="n">
         <v>0.12</v>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="Q50" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="C51" s="10" t="n">
-        <v>24.04</v>
+        <v>23.68</v>
       </c>
       <c r="D51" s="10" t="n">
         <v>24.59</v>
@@ -4295,13 +4295,13 @@
         <v>20.1</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>0.0011</v>
+        <v>0.0049</v>
       </c>
       <c r="G51" s="11" t="n">
-        <v>0.0023</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="H51" s="11" t="n">
-        <v>0.0045</v>
+        <v>0.0198</v>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
@@ -4309,13 +4309,13 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>29.68</v>
+        <v>29.23</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>8.15</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="L51" s="9" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="M51" s="9" t="n">
         <v>2.51</v>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="Q51" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="C52" s="10" t="n">
-        <v>39.76</v>
+        <v>39.72</v>
       </c>
       <c r="D52" s="10" t="n">
         <v>43.79</v>
@@ -4362,13 +4362,13 @@
         <v>26.73</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>-0.0016</v>
+        <v>-0.0005</v>
       </c>
       <c r="G52" s="11" t="n">
-        <v>-0.0032</v>
+        <v>-0.0009</v>
       </c>
       <c r="H52" s="11" t="n">
-        <v>-0.0064</v>
+        <v>-0.0018</v>
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
@@ -4376,10 +4376,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>26.68</v>
+        <v>26.66</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
       <c r="L52" s="9" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="Q52" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
         </is>
       </c>
       <c r="C53" s="10" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="D53" s="10" t="n">
         <v>4.29</v>
@@ -4431,13 +4431,13 @@
         <v>3.56</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>0.0358</v>
+        <v>0.038</v>
       </c>
       <c r="G53" s="11" t="n">
-        <v>0.07149999999999999</v>
+        <v>0.0759</v>
       </c>
       <c r="H53" s="11" t="n">
-        <v>0.1431</v>
+        <v>0.1519</v>
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
@@ -4445,13 +4445,13 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>5.85</v>
+        <v>5.81</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="L53" s="9" t="n">
-        <v>5.45</v>
+        <v>5.41</v>
       </c>
       <c r="M53" s="9" t="n">
         <v>0.54</v>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="Q53" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
         </is>
       </c>
       <c r="C54" s="10" t="n">
-        <v>171.57</v>
+        <v>172.31</v>
       </c>
       <c r="D54" s="10" t="n">
         <v>222.47</v>
@@ -4498,13 +4498,13 @@
         <v>90</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>-0.012</v>
+        <v>-0.0122</v>
       </c>
       <c r="G54" s="11" t="n">
-        <v>-0.0241</v>
+        <v>-0.0245</v>
       </c>
       <c r="H54" s="11" t="n">
-        <v>-0.0481</v>
+        <v>-0.049</v>
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>18.38</v>
+        <v>18.44</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>3.98</v>
+        <v>3.99</v>
       </c>
       <c r="L54" s="9" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="Q54" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
         <v>1.88</v>
       </c>
       <c r="L55" s="9" t="n">
-        <v>3.55</v>
+        <v>3.59</v>
       </c>
       <c r="M55" s="9" t="n">
         <v>6.3</v>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="P55" s="12" t="inlineStr">
         <is>
-          <t>Corporate Travel Management Limited, a travel management solutions company, manages the procurement and delivery of travel services in Australia and New Zealand, North America, Asia, and Europe. . The company provides corporate travels, meetings and event travel management, resources travel, sports travel, leisure travel, loyalty travel, and wholesale travel services, as well as accommodation a...</t>
+          <t>Corporate Travel Management Limited, a travel management solutions company, manages the procurement and delivery of travel services in Australia and New Zealand, North America, Asia, and Europe. The company provides corporate travels, including strategic account management, and small business solutions; meetings and event travel management, resources travel, sports travel, leisure travel, loyal...</t>
         </is>
       </c>
       <c r="Q55" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="C56" s="6" t="n">
-        <v>8.02</v>
+        <v>8.24</v>
       </c>
       <c r="D56" s="6" t="n">
         <v>13.48</v>
@@ -4634,13 +4634,13 @@
         <v>8.01</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>0.3334</v>
+        <v>0.2794</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.5589</v>
       </c>
       <c r="H56" s="7" t="n">
-        <v>1.3336</v>
+        <v>1.1177</v>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
@@ -4648,13 +4648,13 @@
         </is>
       </c>
       <c r="J56" s="5" t="n">
-        <v>11.97</v>
+        <v>12.3</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>4.3</v>
+        <v>4.42</v>
       </c>
       <c r="M56" s="5" t="n">
         <v>0.71</v>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="Q56" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
         </is>
       </c>
       <c r="C57" s="6" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="D57" s="6" t="n">
         <v>2.96</v>
@@ -4701,13 +4701,13 @@
         <v>2.14</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0.0414</v>
+        <v>0.0448</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>0.0829</v>
+        <v>0.0897</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>0.1657</v>
+        <v>0.1793</v>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
@@ -4715,13 +4715,13 @@
         </is>
       </c>
       <c r="J57" s="5" t="n">
-        <v>65</v>
+        <v>64.25</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M57" s="5" t="n">
         <v>0.8</v>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="Q57" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="Q58" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         </is>
       </c>
       <c r="C59" s="10" t="n">
-        <v>20.86</v>
+        <v>20.58</v>
       </c>
       <c r="D59" s="10" t="n">
         <v>24.58</v>
@@ -4843,13 +4843,13 @@
         <v>13.11</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>-0.007</v>
+        <v>-0.0037</v>
       </c>
       <c r="G59" s="11" t="n">
-        <v>-0.0139</v>
+        <v>-0.0073</v>
       </c>
       <c r="H59" s="11" t="n">
-        <v>-0.0279</v>
+        <v>-0.0146</v>
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
@@ -4857,13 +4857,13 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>14.6</v>
+        <v>14.41</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>2.89</v>
+        <v>4.26</v>
       </c>
       <c r="L59" s="9" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="M59" s="9" t="n">
         <v>2.45</v>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="Q59" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="Q60" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
         </is>
       </c>
       <c r="C61" s="10" t="n">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
       <c r="D61" s="10" t="n">
         <v>4.78</v>
@@ -4977,13 +4977,13 @@
         <v>3.67</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>0.0328</v>
+        <v>0.0308</v>
       </c>
       <c r="G61" s="11" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.0616</v>
       </c>
       <c r="H61" s="11" t="n">
-        <v>0.1314</v>
+        <v>0.1232</v>
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
@@ -4991,13 +4991,13 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>13.26</v>
+        <v>13.35</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>15.28</v>
+        <v>15.39</v>
       </c>
       <c r="L61" s="9" t="n">
-        <v>8.98</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="M61" s="9" t="n">
         <v>1</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="Q61" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>5.78</v>
+        <v>5.89</v>
       </c>
       <c r="D62" s="10" t="n">
         <v>7.73</v>
@@ -5044,13 +5044,13 @@
         <v>5.3</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>0.0323</v>
+        <v>0.027</v>
       </c>
       <c r="G62" s="11" t="n">
-        <v>0.0646</v>
+        <v>0.054</v>
       </c>
       <c r="H62" s="11" t="n">
-        <v>0.1292</v>
+        <v>0.1081</v>
       </c>
       <c r="I62" s="9" t="inlineStr">
         <is>
@@ -5058,13 +5058,13 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>10.51</v>
+        <v>10.71</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="L62" s="9" t="n">
-        <v>4.68</v>
+        <v>4.77</v>
       </c>
       <c r="M62" s="9" t="n">
         <v>0.47</v>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="Q62" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -5102,7 +5102,7 @@
         </is>
       </c>
       <c r="C63" s="6" t="n">
-        <v>6.02</v>
+        <v>5.96</v>
       </c>
       <c r="D63" s="6" t="n">
         <v>7.91</v>
@@ -5111,13 +5111,13 @@
         <v>4.96</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>0.0207</v>
+        <v>0.0234</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>0.0413</v>
+        <v>0.0468</v>
       </c>
       <c r="H63" s="7" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.0935</v>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
@@ -5125,13 +5125,13 @@
         </is>
       </c>
       <c r="J63" s="5" t="n">
-        <v>24.08</v>
+        <v>23.84</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
       <c r="M63" s="5" t="n">
         <v>0.79</v>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -5172,7 +5172,7 @@
         <v>0.245</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>1.145</v>
+        <v>1.09</v>
       </c>
       <c r="E64" s="6" t="n">
         <v>0.22</v>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="Q64" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
         </is>
       </c>
       <c r="C65" s="10" t="n">
-        <v>14.88</v>
+        <v>14.92</v>
       </c>
       <c r="D65" s="10" t="n">
         <v>17.75</v>
@@ -5245,13 +5245,13 @@
         <v>8.855</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>-0.0305</v>
+        <v>-0.0311</v>
       </c>
       <c r="G65" s="11" t="n">
-        <v>-0.061</v>
+        <v>-0.0622</v>
       </c>
       <c r="H65" s="11" t="n">
-        <v>-0.122</v>
+        <v>-0.1243</v>
       </c>
       <c r="I65" s="9" t="inlineStr">
         <is>
@@ -5259,13 +5259,13 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>20.38</v>
+        <v>20.44</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>5.18</v>
+        <v>5.2</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>5.47</v>
+        <v>5.49</v>
       </c>
       <c r="M65" s="9" t="n">
         <v>0.25</v>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="Q65" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -5303,7 +5303,7 @@
         </is>
       </c>
       <c r="C66" s="10" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="D66" s="10" t="n">
         <v>3.44</v>
@@ -5312,13 +5312,13 @@
         <v>2.22</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>-0.0133</v>
+        <v>-0.0104</v>
       </c>
       <c r="G66" s="11" t="n">
-        <v>-0.0265</v>
+        <v>-0.0207</v>
       </c>
       <c r="H66" s="11" t="n">
-        <v>-0.053</v>
+        <v>-0.0414</v>
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
@@ -5326,13 +5326,13 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>22</v>
+        <v>21.73</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
       <c r="M66" s="9" t="n">
         <v>0.51</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="Q66" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="C67" s="6" t="n">
-        <v>11.78</v>
+        <v>11.74</v>
       </c>
       <c r="D67" s="6" t="n">
         <v>16.56</v>
@@ -5379,13 +5379,13 @@
         <v>9.609999999999999</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>0.0525</v>
+        <v>0.0536</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>0.1051</v>
+        <v>0.1071</v>
       </c>
       <c r="H67" s="7" t="n">
-        <v>0.2102</v>
+        <v>0.2143</v>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
@@ -5393,13 +5393,13 @@
         </is>
       </c>
       <c r="J67" s="5" t="n">
-        <v>16.83</v>
+        <v>16.77</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="M67" s="5" t="n">
         <v>1.12</v>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -5437,22 +5437,22 @@
         </is>
       </c>
       <c r="C68" s="10" t="n">
-        <v>17.7</v>
+        <v>17.41</v>
       </c>
       <c r="D68" s="10" t="n">
         <v>23.38</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>17.435</v>
+        <v>17.1</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>-0.0058</v>
+        <v>-0.0009</v>
       </c>
       <c r="G68" s="11" t="n">
-        <v>-0.0116</v>
+        <v>-0.0017</v>
       </c>
       <c r="H68" s="11" t="n">
-        <v>-0.0231</v>
+        <v>-0.0034</v>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
@@ -5460,13 +5460,13 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>13.62</v>
+        <v>13.39</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="L68" s="9" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="M68" s="9" t="n">
         <v>0.29</v>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Q68" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="C69" s="6" t="n">
-        <v>36.33</v>
+        <v>36.5</v>
       </c>
       <c r="D69" s="6" t="n">
         <v>37.71</v>
@@ -5513,13 +5513,13 @@
         <v>26.51</v>
       </c>
       <c r="F69" s="7" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>0.0199</v>
+        <v>0.0167</v>
       </c>
       <c r="H69" s="7" t="n">
-        <v>0.0398</v>
+        <v>0.0334</v>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
@@ -5527,13 +5527,13 @@
         </is>
       </c>
       <c r="J69" s="5" t="n">
-        <v>55.05</v>
+        <v>55.3</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>12.22</v>
+        <v>12.28</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>9.24</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="M69" s="5" t="n">
         <v>6.91</v>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="C70" s="6" t="n">
-        <v>27.73</v>
+        <v>27.47</v>
       </c>
       <c r="D70" s="6" t="n">
         <v>34.78</v>
@@ -5580,13 +5580,13 @@
         <v>24.56</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>0.063</v>
+        <v>0.0659</v>
       </c>
       <c r="G70" s="7" t="n">
-        <v>0.1259</v>
+        <v>0.1318</v>
       </c>
       <c r="H70" s="7" t="n">
-        <v>0.2518</v>
+        <v>0.2637</v>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
@@ -5594,15 +5594,13 @@
         </is>
       </c>
       <c r="J70" s="5" t="n">
-        <v>20.85</v>
+        <v>20.65</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="L70" s="5" t="inlineStr">
-        <is>
-          <t>No data</t>
-        </is>
+        <v>2.25</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>13.9</v>
       </c>
       <c r="M70" s="5" t="n">
         <v>0.24</v>
@@ -5624,7 +5622,7 @@
       </c>
       <c r="Q70" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5638,7 @@
         </is>
       </c>
       <c r="C71" s="10" t="n">
-        <v>6.18</v>
+        <v>6.26</v>
       </c>
       <c r="D71" s="10" t="n">
         <v>9.130000000000001</v>
@@ -5649,13 +5647,13 @@
         <v>4.69</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>0.0037</v>
+        <v>0.0004</v>
       </c>
       <c r="G71" s="11" t="n">
-        <v>0.0073</v>
+        <v>0.0008</v>
       </c>
       <c r="H71" s="11" t="n">
-        <v>0.0146</v>
+        <v>0.0017</v>
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
@@ -5663,13 +5661,13 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>27.93</v>
+        <v>28.29</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="L71" s="9" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="M71" s="9" t="n">
         <v>1.41</v>
@@ -5691,7 +5689,7 @@
       </c>
       <c r="Q71" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5764,7 @@
       </c>
       <c r="Q72" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5780,7 @@
         </is>
       </c>
       <c r="C73" s="6" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="D73" s="6" t="n">
         <v>2.68</v>
@@ -5791,13 +5789,13 @@
         <v>2.05</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>0.0673</v>
+        <v>0.0688</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>0.1346</v>
+        <v>0.1377</v>
       </c>
       <c r="H73" s="7" t="n">
-        <v>0.2692</v>
+        <v>0.2754</v>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
@@ -5805,13 +5803,13 @@
         </is>
       </c>
       <c r="J73" s="5" t="n">
-        <v>17.33</v>
+        <v>17.25</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>4.71</v>
+        <v>4.68</v>
       </c>
       <c r="M73" s="5" t="n">
         <v>0.84</v>
@@ -5833,7 +5831,7 @@
       </c>
       <c r="Q73" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5847,7 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>4.7</v>
+        <v>4.72</v>
       </c>
       <c r="D74" s="10" t="n">
         <v>5.75</v>
@@ -5858,13 +5856,13 @@
         <v>4.42</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>0.04</v>
+        <v>0.0388</v>
       </c>
       <c r="G74" s="11" t="n">
-        <v>0.08</v>
+        <v>0.0776</v>
       </c>
       <c r="H74" s="11" t="n">
-        <v>0.1601</v>
+        <v>0.1552</v>
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
@@ -5872,13 +5870,13 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>8.550000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="K74" s="9" t="n">
         <v>0.84</v>
       </c>
       <c r="L74" s="9" t="n">
-        <v>9.07</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="M74" s="9" t="n">
         <v>0.53</v>
@@ -5900,7 +5898,7 @@
       </c>
       <c r="Q74" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -5975,7 +5973,7 @@
       </c>
       <c r="Q75" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6040,7 @@
       </c>
       <c r="Q76" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -6058,7 +6056,7 @@
         </is>
       </c>
       <c r="C77" s="6" t="n">
-        <v>75.79000000000001</v>
+        <v>73.78</v>
       </c>
       <c r="D77" s="6" t="n">
         <v>122.03</v>
@@ -6067,13 +6065,13 @@
         <v>68.7</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>0.1363</v>
+        <v>0.1536</v>
       </c>
       <c r="H77" s="7" t="n">
-        <v>0.2725</v>
+        <v>0.3072</v>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
@@ -6081,13 +6079,13 @@
         </is>
       </c>
       <c r="J77" s="5" t="n">
-        <v>51.91</v>
+        <v>50.53</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>11.18</v>
+        <v>10.88</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>12.47</v>
+        <v>12.14</v>
       </c>
       <c r="M77" s="5" t="n">
         <v>0.13</v>
@@ -6109,7 +6107,7 @@
       </c>
       <c r="Q77" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -6125,22 +6123,22 @@
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>4.28</v>
+        <v>4.17</v>
       </c>
       <c r="D78" s="10" t="n">
         <v>7.7</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>4.28</v>
+        <v>4.15</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>0.0327</v>
+        <v>0.0342</v>
       </c>
       <c r="G78" s="11" t="n">
-        <v>0.0654</v>
+        <v>0.0683</v>
       </c>
       <c r="H78" s="11" t="n">
-        <v>0.1308</v>
+        <v>0.1367</v>
       </c>
       <c r="I78" s="9" t="inlineStr">
         <is>
@@ -6148,13 +6146,13 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>10.19</v>
+        <v>9.93</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="L78" s="9" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="M78" s="9" t="n">
         <v>0.52</v>
@@ -6176,7 +6174,7 @@
       </c>
       <c r="Q78" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -6192,22 +6190,22 @@
         </is>
       </c>
       <c r="C79" s="10" t="n">
-        <v>7.85</v>
+        <v>7.87</v>
       </c>
       <c r="D79" s="10" t="n">
-        <v>8.84</v>
+        <v>8.82</v>
       </c>
       <c r="E79" s="10" t="n">
         <v>6.39</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>0.014</v>
+        <v>0.0133</v>
       </c>
       <c r="G79" s="11" t="n">
-        <v>0.028</v>
+        <v>0.0267</v>
       </c>
       <c r="H79" s="11" t="n">
-        <v>0.0561</v>
+        <v>0.0534</v>
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
@@ -6215,7 +6213,7 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>18.26</v>
+        <v>18.3</v>
       </c>
       <c r="K79" s="9" t="n">
         <v>2.53</v>
@@ -6245,7 +6243,7 @@
       </c>
       <c r="Q79" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6259,7 @@
         </is>
       </c>
       <c r="C80" s="10" t="n">
-        <v>1.765</v>
+        <v>1.73</v>
       </c>
       <c r="D80" s="10" t="n">
         <v>6.735</v>
@@ -6270,13 +6268,13 @@
         <v>1.53</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>0.1605</v>
+        <v>0.1689</v>
       </c>
       <c r="G80" s="11" t="n">
-        <v>0.3211</v>
+        <v>0.3377</v>
       </c>
       <c r="H80" s="11" t="n">
-        <v>0.6422</v>
+        <v>0.6754</v>
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
@@ -6284,13 +6282,13 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>44.12</v>
+        <v>43.25</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="L80" s="9" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
       <c r="M80" s="9" t="n">
         <v>0.84</v>
@@ -6312,7 +6310,7 @@
       </c>
       <c r="Q80" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -6387,7 +6385,7 @@
       </c>
       <c r="Q81" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -6403,7 +6401,7 @@
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>8.69</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="D82" s="10" t="n">
         <v>10.05</v>
@@ -6412,13 +6410,13 @@
         <v>4.1</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>-0.0293</v>
+        <v>-0.0244</v>
       </c>
       <c r="G82" s="11" t="n">
-        <v>-0.0586</v>
+        <v>-0.0488</v>
       </c>
       <c r="H82" s="11" t="n">
-        <v>-0.1172</v>
+        <v>-0.0975</v>
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
@@ -6426,13 +6424,13 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>45.74</v>
+        <v>44.95</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>3.19</v>
+        <v>3.13</v>
       </c>
       <c r="L82" s="9" t="n">
-        <v>14.22</v>
+        <v>13.97</v>
       </c>
       <c r="M82" s="9" t="n">
         <v>0.75</v>
@@ -6454,7 +6452,7 @@
       </c>
       <c r="Q82" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6468,7 @@
         </is>
       </c>
       <c r="C83" s="6" t="n">
-        <v>6.86</v>
+        <v>6.95</v>
       </c>
       <c r="D83" s="6" t="n">
         <v>9.48</v>
@@ -6479,13 +6477,13 @@
         <v>4.92</v>
       </c>
       <c r="F83" s="7" t="n">
-        <v>0.0425</v>
+        <v>0.0387</v>
       </c>
       <c r="G83" s="7" t="n">
-        <v>0.0849</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="H83" s="7" t="n">
-        <v>0.1698</v>
+        <v>0.1547</v>
       </c>
       <c r="I83" s="5" t="inlineStr">
         <is>
@@ -6493,13 +6491,13 @@
         </is>
       </c>
       <c r="J83" s="5" t="n">
-        <v>-23.18</v>
+        <v>-23.48</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="M83" s="5" t="n">
         <v>0.63</v>
@@ -6521,7 +6519,7 @@
       </c>
       <c r="Q83" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -6537,22 +6535,22 @@
         </is>
       </c>
       <c r="C84" s="6" t="n">
-        <v>3.66</v>
+        <v>3.57</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>5.94</v>
+        <v>5.88</v>
       </c>
       <c r="E84" s="6" t="n">
-        <v>3.62</v>
+        <v>3.53</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>0.09569999999999999</v>
+        <v>0.104</v>
       </c>
       <c r="G84" s="7" t="n">
-        <v>0.1914</v>
+        <v>0.208</v>
       </c>
       <c r="H84" s="7" t="n">
-        <v>0.3829</v>
+        <v>0.416</v>
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
@@ -6560,13 +6558,13 @@
         </is>
       </c>
       <c r="J84" s="5" t="n">
-        <v>8.130000000000001</v>
+        <v>7.93</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>0.89</v>
+        <v>0.83</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="M84" s="5" t="n">
         <v>0.58</v>
@@ -6588,7 +6586,7 @@
       </c>
       <c r="Q84" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -6604,22 +6602,22 @@
         </is>
       </c>
       <c r="C85" s="10" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="D85" s="10" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="E85" s="10" t="n">
         <v>1.69</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>0.0286</v>
+        <v>0.0232</v>
       </c>
       <c r="G85" s="11" t="n">
-        <v>0.0572</v>
+        <v>0.0464</v>
       </c>
       <c r="H85" s="11" t="n">
-        <v>0.1144</v>
+        <v>0.0929</v>
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
@@ -6627,13 +6625,13 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>22.56</v>
+        <v>23</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="L85" s="9" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="M85" s="9" t="n">
         <v>6.18</v>
@@ -6655,7 +6653,7 @@
       </c>
       <c r="Q85" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -6671,22 +6669,22 @@
         </is>
       </c>
       <c r="C86" s="10" t="n">
-        <v>3.34</v>
+        <v>3.37</v>
       </c>
       <c r="D86" s="10" t="n">
-        <v>4.57</v>
+        <v>4.52</v>
       </c>
       <c r="E86" s="10" t="n">
         <v>3.155</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G86" s="11" t="n">
-        <v>0.1438</v>
+        <v>0.1381</v>
       </c>
       <c r="H86" s="11" t="n">
-        <v>0.2876</v>
+        <v>0.2761</v>
       </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
@@ -6694,13 +6692,13 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>10.77</v>
+        <v>10.87</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="L86" s="9" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M86" s="9" t="n">
         <v>0.67</v>
@@ -6722,7 +6720,7 @@
       </c>
       <c r="Q86" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6795,7 @@
       </c>
       <c r="Q87" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -6813,22 +6811,22 @@
         </is>
       </c>
       <c r="C88" s="6" t="n">
-        <v>5.68</v>
+        <v>5.54</v>
       </c>
       <c r="D88" s="6" t="n">
         <v>10.38</v>
       </c>
       <c r="E88" s="6" t="n">
-        <v>5.64</v>
+        <v>5.5</v>
       </c>
       <c r="F88" s="7" t="n">
-        <v>0.1376</v>
+        <v>0.1474</v>
       </c>
       <c r="G88" s="7" t="n">
-        <v>0.2752</v>
+        <v>0.2948</v>
       </c>
       <c r="H88" s="7" t="n">
-        <v>0.5504</v>
+        <v>0.5896</v>
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
@@ -6836,13 +6834,13 @@
         </is>
       </c>
       <c r="J88" s="5" t="n">
-        <v>11.83</v>
+        <v>11.54</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="M88" s="5" t="n">
         <v>0.41</v>
@@ -6864,7 +6862,7 @@
       </c>
       <c r="Q88" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -6939,7 +6937,7 @@
       </c>
       <c r="Q89" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -6955,22 +6953,22 @@
         </is>
       </c>
       <c r="C90" s="10" t="n">
-        <v>66.90000000000001</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="D90" s="10" t="n">
         <v>120</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>66.02</v>
+        <v>65.66</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>0.0361</v>
+        <v>0.0376</v>
       </c>
       <c r="G90" s="11" t="n">
-        <v>0.0723</v>
+        <v>0.0751</v>
       </c>
       <c r="H90" s="11" t="n">
-        <v>0.1446</v>
+        <v>0.1502</v>
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
@@ -6978,10 +6976,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>14.97</v>
+        <v>14.89</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>4.46</v>
+        <v>4.44</v>
       </c>
       <c r="L90" s="9" t="n">
         <v>0.66</v>
@@ -7006,7 +7004,7 @@
       </c>
       <c r="Q90" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7079,7 @@
       </c>
       <c r="Q91" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -7097,7 +7095,7 @@
         </is>
       </c>
       <c r="C92" s="6" t="n">
-        <v>41.49</v>
+        <v>41.38</v>
       </c>
       <c r="D92" s="6" t="n">
         <v>44.12</v>
@@ -7106,13 +7104,13 @@
         <v>24.41</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>0.02</v>
+        <v>0.0217</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>0.04</v>
+        <v>0.0433</v>
       </c>
       <c r="H92" s="7" t="n">
-        <v>0.0801</v>
+        <v>0.0867</v>
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
@@ -7120,13 +7118,13 @@
         </is>
       </c>
       <c r="J92" s="5" t="n">
-        <v>133.84</v>
+        <v>133.48</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>4.45</v>
+        <v>4.44</v>
       </c>
       <c r="M92" s="5" t="n">
         <v>0.6899999999999999</v>
@@ -7148,7 +7146,7 @@
       </c>
       <c r="Q92" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7162,7 @@
         </is>
       </c>
       <c r="C93" s="6" t="n">
-        <v>4.25</v>
+        <v>4.17</v>
       </c>
       <c r="D93" s="6" t="n">
         <v>5.25</v>
@@ -7173,13 +7171,13 @@
         <v>3.68</v>
       </c>
       <c r="F93" s="7" t="n">
-        <v>0.0597</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="G93" s="7" t="n">
-        <v>0.1193</v>
+        <v>0.1312</v>
       </c>
       <c r="H93" s="7" t="n">
-        <v>0.2387</v>
+        <v>0.2624</v>
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
@@ -7187,13 +7185,13 @@
         </is>
       </c>
       <c r="J93" s="5" t="n">
-        <v>18.48</v>
+        <v>18.13</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="M93" s="5" t="n">
         <v>1.11</v>
@@ -7215,7 +7213,7 @@
       </c>
       <c r="Q93" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7229,7 @@
         </is>
       </c>
       <c r="C94" s="10" t="n">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="D94" s="10" t="n">
         <v>5.85</v>
@@ -7240,13 +7238,13 @@
         <v>2.4</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>0.0555</v>
+        <v>0.0474</v>
       </c>
       <c r="G94" s="11" t="n">
-        <v>0.111</v>
+        <v>0.0948</v>
       </c>
       <c r="H94" s="11" t="n">
-        <v>0.2221</v>
+        <v>0.1897</v>
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
@@ -7254,13 +7252,13 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>11.86</v>
+        <v>12.18</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="L94" s="9" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="M94" s="9" t="n">
         <v>0.97</v>
@@ -7282,7 +7280,7 @@
       </c>
       <c r="Q94" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -7357,7 +7355,7 @@
       </c>
       <c r="Q95" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7371,7 @@
         </is>
       </c>
       <c r="C96" s="10" t="n">
-        <v>15.94</v>
+        <v>15.49</v>
       </c>
       <c r="D96" s="10" t="n">
         <v>22.37</v>
@@ -7382,13 +7380,13 @@
         <v>12.15</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>0.0311</v>
+        <v>0.0393</v>
       </c>
       <c r="G96" s="11" t="n">
-        <v>0.0623</v>
+        <v>0.0786</v>
       </c>
       <c r="H96" s="11" t="n">
-        <v>0.1245</v>
+        <v>0.1572</v>
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
@@ -7396,13 +7394,13 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>72.45</v>
+        <v>70.41</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>4.77</v>
+        <v>4.63</v>
       </c>
       <c r="L96" s="9" t="n">
-        <v>16.41</v>
+        <v>15.94</v>
       </c>
       <c r="M96" s="9" t="n">
         <v>9.69</v>
@@ -7424,7 +7422,7 @@
       </c>
       <c r="Q96" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7438,7 @@
         </is>
       </c>
       <c r="C97" s="10" t="n">
-        <v>8.98</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D97" s="10" t="n">
         <v>11.55</v>
@@ -7449,13 +7447,13 @@
         <v>7.96</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>0.0066</v>
+        <v>0.0101</v>
       </c>
       <c r="G97" s="11" t="n">
-        <v>0.0133</v>
+        <v>0.0202</v>
       </c>
       <c r="H97" s="11" t="n">
-        <v>0.0266</v>
+        <v>0.0403</v>
       </c>
       <c r="I97" s="9" t="inlineStr">
         <is>
@@ -7463,13 +7461,13 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>17.96</v>
+        <v>17.4</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="L97" s="9" t="n">
-        <v>13.34</v>
+        <v>12.93</v>
       </c>
       <c r="M97" s="9" t="n">
         <v>0.19</v>
@@ -7491,7 +7489,7 @@
       </c>
       <c r="Q97" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -7507,7 +7505,7 @@
         </is>
       </c>
       <c r="C98" s="6" t="n">
-        <v>1.82</v>
+        <v>1.855</v>
       </c>
       <c r="D98" s="6" t="n">
         <v>2.46</v>
@@ -7516,13 +7514,13 @@
         <v>1.607</v>
       </c>
       <c r="F98" s="7" t="n">
-        <v>0.0416</v>
+        <v>0.0361</v>
       </c>
       <c r="G98" s="7" t="n">
-        <v>0.0832</v>
+        <v>0.0722</v>
       </c>
       <c r="H98" s="7" t="n">
-        <v>0.1663</v>
+        <v>0.1443</v>
       </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
@@ -7530,13 +7528,13 @@
         </is>
       </c>
       <c r="J98" s="5" t="n">
-        <v>10.71</v>
+        <v>10.91</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="M98" s="5" t="n">
         <v>0.42</v>
@@ -7558,7 +7556,7 @@
       </c>
       <c r="Q98" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7572,7 @@
         </is>
       </c>
       <c r="C99" s="10" t="n">
-        <v>64.63</v>
+        <v>65</v>
       </c>
       <c r="D99" s="10" t="n">
         <v>74.94</v>
@@ -7583,13 +7581,13 @@
         <v>34.12</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>0.0131</v>
+        <v>0.0116</v>
       </c>
       <c r="G99" s="11" t="n">
-        <v>0.0261</v>
+        <v>0.0231</v>
       </c>
       <c r="H99" s="11" t="n">
-        <v>0.0523</v>
+        <v>0.0463</v>
       </c>
       <c r="I99" s="9" t="inlineStr">
         <is>
@@ -7597,13 +7595,13 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>12.13</v>
+        <v>12.2</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="L99" s="9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="M99" s="9" t="n">
         <v>1.21</v>
@@ -7625,7 +7623,7 @@
       </c>
       <c r="Q99" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:45</t>
         </is>
       </c>
     </row>
@@ -7641,7 +7639,7 @@
         </is>
       </c>
       <c r="C100" s="10" t="n">
-        <v>4.84</v>
+        <v>4.81</v>
       </c>
       <c r="D100" s="10" t="n">
         <v>5.31</v>
@@ -7650,13 +7648,13 @@
         <v>4.06</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>0.0137</v>
+        <v>0.0153</v>
       </c>
       <c r="G100" s="11" t="n">
-        <v>0.0274</v>
+        <v>0.0307</v>
       </c>
       <c r="H100" s="11" t="n">
-        <v>0.0548</v>
+        <v>0.0613</v>
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
@@ -7664,13 +7662,13 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>21.04</v>
+        <v>20.91</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>5.48</v>
+        <v>5.45</v>
       </c>
       <c r="L100" s="9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M100" s="9" t="n">
         <v>0.11</v>
@@ -7692,7 +7690,7 @@
       </c>
       <c r="Q100" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -7708,7 +7706,7 @@
         </is>
       </c>
       <c r="C101" s="10" t="n">
-        <v>250.59</v>
+        <v>247.57</v>
       </c>
       <c r="D101" s="10" t="n">
         <v>267.905</v>
@@ -7767,7 +7765,7 @@
       </c>
       <c r="Q101" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -7783,7 +7781,7 @@
         </is>
       </c>
       <c r="C102" s="10" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="D102" s="10" t="n">
         <v>4.26</v>
@@ -7792,13 +7790,13 @@
         <v>2.63</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>0.0446</v>
+        <v>0.0387</v>
       </c>
       <c r="G102" s="11" t="n">
-        <v>0.0891</v>
+        <v>0.0774</v>
       </c>
       <c r="H102" s="11" t="n">
-        <v>0.1783</v>
+        <v>0.1547</v>
       </c>
       <c r="I102" s="9" t="inlineStr">
         <is>
@@ -7806,10 +7804,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>11.76</v>
+        <v>12</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="L102" s="9" t="inlineStr">
         <is>
@@ -7836,7 +7834,7 @@
       </c>
       <c r="Q102" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -7852,7 +7850,7 @@
         </is>
       </c>
       <c r="C103" s="10" t="n">
-        <v>38.63</v>
+        <v>38.5</v>
       </c>
       <c r="D103" s="10" t="n">
         <v>49.45</v>
@@ -7861,13 +7859,13 @@
         <v>35.48</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>-0.0016</v>
+        <v>-0.0008</v>
       </c>
       <c r="G103" s="11" t="n">
-        <v>-0.0032</v>
+        <v>-0.0015</v>
       </c>
       <c r="H103" s="11" t="n">
-        <v>-0.0064</v>
+        <v>-0.0031</v>
       </c>
       <c r="I103" s="9" t="inlineStr">
         <is>
@@ -7875,7 +7873,7 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>19.32</v>
+        <v>19.25</v>
       </c>
       <c r="K103" s="9" t="n">
         <v>1.95</v>
@@ -7907,7 +7905,7 @@
       </c>
       <c r="Q103" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7921,7 @@
         </is>
       </c>
       <c r="C104" s="6" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="D104" s="6" t="n">
         <v>4.76</v>
@@ -7932,13 +7930,13 @@
         <v>2.65</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>0.099</v>
+        <v>0.1067</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>0.1979</v>
+        <v>0.2134</v>
       </c>
       <c r="H104" s="7" t="n">
-        <v>0.3958</v>
+        <v>0.4269</v>
       </c>
       <c r="I104" s="5" t="inlineStr">
         <is>
@@ -7946,13 +7944,13 @@
         </is>
       </c>
       <c r="J104" s="5" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="M104" s="5" t="n">
         <v>0.11</v>
@@ -7974,7 +7972,7 @@
       </c>
       <c r="Q104" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -7990,7 +7988,7 @@
         </is>
       </c>
       <c r="C105" s="6" t="n">
-        <v>0.965</v>
+        <v>0.975</v>
       </c>
       <c r="D105" s="6" t="n">
         <v>1.77</v>
@@ -7999,13 +7997,13 @@
         <v>0.835</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="G105" s="7" t="n">
-        <v>0.1759</v>
+        <v>0.1689</v>
       </c>
       <c r="H105" s="7" t="n">
-        <v>0.3518</v>
+        <v>0.3379</v>
       </c>
       <c r="I105" s="5" t="inlineStr">
         <is>
@@ -8013,10 +8011,10 @@
         </is>
       </c>
       <c r="J105" s="5" t="n">
-        <v>9.279999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="K105" s="5" t="n">
-        <v>0.93</v>
+        <v>1.31</v>
       </c>
       <c r="L105" s="5" t="n">
         <v>0.7</v>
@@ -8041,7 +8039,7 @@
       </c>
       <c r="Q105" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -8057,7 +8055,7 @@
         </is>
       </c>
       <c r="C106" s="10" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="D106" s="10" t="n">
         <v>7.73</v>
@@ -8066,13 +8064,13 @@
         <v>5.79</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>0.0298</v>
+        <v>0.0257</v>
       </c>
       <c r="G106" s="11" t="n">
-        <v>0.0596</v>
+        <v>0.0514</v>
       </c>
       <c r="H106" s="11" t="n">
-        <v>0.1191</v>
+        <v>0.1029</v>
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
@@ -8080,13 +8078,13 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>17.89</v>
+        <v>18.16</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="L106" s="9" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="M106" s="9" t="n">
         <v>0.2</v>
@@ -8108,7 +8106,7 @@
       </c>
       <c r="Q106" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -8183,7 +8181,7 @@
       </c>
       <c r="Q107" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -8199,7 +8197,7 @@
         </is>
       </c>
       <c r="C108" s="10" t="n">
-        <v>23.44</v>
+        <v>23.69</v>
       </c>
       <c r="D108" s="10" t="n">
         <v>31.96</v>
@@ -8208,13 +8206,13 @@
         <v>17.07</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>0.0055</v>
+        <v>0.0028</v>
       </c>
       <c r="G108" s="11" t="n">
-        <v>0.011</v>
+        <v>0.0056</v>
       </c>
       <c r="H108" s="11" t="n">
-        <v>0.022</v>
+        <v>0.0113</v>
       </c>
       <c r="I108" s="9" t="inlineStr">
         <is>
@@ -8222,13 +8220,13 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>20.21</v>
+        <v>20.42</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="L108" s="9" t="n">
-        <v>4.38</v>
+        <v>4.43</v>
       </c>
       <c r="M108" s="9" t="n">
         <v>0.11</v>
@@ -8250,7 +8248,7 @@
       </c>
       <c r="Q108" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -8266,22 +8264,22 @@
         </is>
       </c>
       <c r="C109" s="10" t="n">
-        <v>3.17</v>
+        <v>3.3</v>
       </c>
       <c r="D109" s="10" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="E109" s="10" t="n">
         <v>1.79</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>0.0241</v>
+        <v>0.0133</v>
       </c>
       <c r="G109" s="11" t="n">
-        <v>0.0481</v>
+        <v>0.0265</v>
       </c>
       <c r="H109" s="11" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.053</v>
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
@@ -8289,10 +8287,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>16.24</v>
+        <v>16.9</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="L109" s="9" t="inlineStr">
         <is>
@@ -8319,7 +8317,7 @@
       </c>
       <c r="Q109" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -8335,22 +8333,22 @@
         </is>
       </c>
       <c r="C110" s="10" t="n">
-        <v>21.56</v>
+        <v>20.72</v>
       </c>
       <c r="D110" s="10" t="n">
-        <v>34.5</v>
+        <v>33.62</v>
       </c>
       <c r="E110" s="10" t="n">
         <v>19.805</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>0.0626</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="G110" s="11" t="n">
-        <v>0.1252</v>
+        <v>0.1506</v>
       </c>
       <c r="H110" s="11" t="n">
-        <v>0.2504</v>
+        <v>0.3011</v>
       </c>
       <c r="I110" s="9" t="inlineStr">
         <is>
@@ -8358,13 +8356,13 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>86.23999999999999</v>
+        <v>82.88</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>35.34</v>
+        <v>33.97</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>13.58</v>
+        <v>13.05</v>
       </c>
       <c r="M110" s="9" t="n">
         <v>0.43</v>
@@ -8386,7 +8384,7 @@
       </c>
       <c r="Q110" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -8402,7 +8400,7 @@
         </is>
       </c>
       <c r="C111" s="6" t="n">
-        <v>48.74</v>
+        <v>47.95</v>
       </c>
       <c r="D111" s="6" t="n">
         <v>52.6</v>
@@ -8411,13 +8409,13 @@
         <v>36.01</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>0.0268</v>
+        <v>0.0324</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>0.0537</v>
+        <v>0.0648</v>
       </c>
       <c r="H111" s="7" t="n">
-        <v>0.1074</v>
+        <v>0.1295</v>
       </c>
       <c r="I111" s="5" t="inlineStr">
         <is>
@@ -8425,13 +8423,13 @@
         </is>
       </c>
       <c r="J111" s="5" t="n">
-        <v>33.85</v>
+        <v>33.3</v>
       </c>
       <c r="K111" s="5" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="M111" s="5" t="n">
         <v>0.32</v>
@@ -8453,7 +8451,7 @@
       </c>
       <c r="Q111" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -8469,7 +8467,7 @@
         </is>
       </c>
       <c r="C112" s="6" t="n">
-        <v>13.81</v>
+        <v>13.23</v>
       </c>
       <c r="D112" s="6" t="n">
         <v>18.22</v>
@@ -8478,13 +8476,13 @@
         <v>10.91</v>
       </c>
       <c r="F112" s="7" t="n">
-        <v>0.1157</v>
+        <v>0.1351</v>
       </c>
       <c r="G112" s="7" t="n">
-        <v>0.2314</v>
+        <v>0.2701</v>
       </c>
       <c r="H112" s="7" t="n">
-        <v>0.4627</v>
+        <v>0.5403</v>
       </c>
       <c r="I112" s="5" t="inlineStr">
         <is>
@@ -8492,13 +8490,13 @@
         </is>
       </c>
       <c r="J112" s="5" t="n">
-        <v>115.08</v>
+        <v>110.25</v>
       </c>
       <c r="K112" s="5" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>21.15</v>
+        <v>20.26</v>
       </c>
       <c r="M112" s="5" t="n">
         <v>0.55</v>
@@ -8520,7 +8518,7 @@
       </c>
       <c r="Q112" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -8536,7 +8534,7 @@
         </is>
       </c>
       <c r="C113" s="10" t="n">
-        <v>1.46</v>
+        <v>1.495</v>
       </c>
       <c r="D113" s="10" t="n">
         <v>2.43</v>
@@ -8545,13 +8543,13 @@
         <v>1.212</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>0.0356</v>
+        <v>0.0289</v>
       </c>
       <c r="G113" s="11" t="n">
-        <v>0.0712</v>
+        <v>0.0579</v>
       </c>
       <c r="H113" s="11" t="n">
-        <v>0.1425</v>
+        <v>0.1157</v>
       </c>
       <c r="I113" s="9" t="inlineStr">
         <is>
@@ -8559,13 +8557,13 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>12.57</v>
+        <v>12.87</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="L113" s="9" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="M113" s="9" t="n">
         <v>0.6</v>
@@ -8587,7 +8585,7 @@
       </c>
       <c r="Q113" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -8603,22 +8601,22 @@
         </is>
       </c>
       <c r="C114" s="10" t="n">
-        <v>11.62</v>
+        <v>11.7</v>
       </c>
       <c r="D114" s="10" t="n">
-        <v>12.995</v>
+        <v>12.99</v>
       </c>
       <c r="E114" s="10" t="n">
         <v>10.02</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0067</v>
       </c>
       <c r="G114" s="11" t="n">
-        <v>0.017</v>
+        <v>0.0135</v>
       </c>
       <c r="H114" s="11" t="n">
-        <v>0.034</v>
+        <v>0.027</v>
       </c>
       <c r="I114" s="9" t="inlineStr">
         <is>
@@ -8626,13 +8624,13 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>12.77</v>
+        <v>12.86</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="L114" s="9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M114" s="9" t="n">
         <v>0.49</v>
@@ -8654,7 +8652,7 @@
       </c>
       <c r="Q114" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -8670,7 +8668,7 @@
         </is>
       </c>
       <c r="C115" s="10" t="n">
-        <v>22.23</v>
+        <v>22.56</v>
       </c>
       <c r="D115" s="10" t="n">
         <v>26.47</v>
@@ -8679,13 +8677,13 @@
         <v>18.58</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>0.041</v>
+        <v>0.0367</v>
       </c>
       <c r="G115" s="11" t="n">
-        <v>0.082</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="H115" s="11" t="n">
-        <v>0.1639</v>
+        <v>0.1469</v>
       </c>
       <c r="I115" s="9" t="inlineStr">
         <is>
@@ -8693,10 +8691,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>43.59</v>
+        <v>44.24</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="L115" s="9" t="inlineStr">
         <is>
@@ -8723,7 +8721,7 @@
       </c>
       <c r="Q115" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8796,7 @@
       </c>
       <c r="Q116" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -8814,7 +8812,7 @@
         </is>
       </c>
       <c r="C117" s="10" t="n">
-        <v>5.4</v>
+        <v>5.48</v>
       </c>
       <c r="D117" s="10" t="n">
         <v>6.81</v>
@@ -8823,13 +8821,13 @@
         <v>1.915</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0128</v>
       </c>
       <c r="G117" s="11" t="n">
-        <v>-0.0185</v>
+        <v>-0.0255</v>
       </c>
       <c r="H117" s="11" t="n">
-        <v>-0.037</v>
+        <v>-0.0511</v>
       </c>
       <c r="I117" s="9" t="inlineStr">
         <is>
@@ -8837,13 +8835,13 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>33.75</v>
+        <v>34.25</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="L117" s="9" t="n">
-        <v>9</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="M117" s="9" t="n">
         <v>0.3</v>
@@ -8865,7 +8863,7 @@
       </c>
       <c r="Q117" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -8881,7 +8879,7 @@
         </is>
       </c>
       <c r="C118" s="10" t="n">
-        <v>179.39</v>
+        <v>176.42</v>
       </c>
       <c r="D118" s="10" t="n">
         <v>321.57</v>
@@ -8890,13 +8888,13 @@
         <v>107.75</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>0.0322</v>
+        <v>0.0369</v>
       </c>
       <c r="G118" s="11" t="n">
-        <v>0.0643</v>
+        <v>0.0738</v>
       </c>
       <c r="H118" s="11" t="n">
-        <v>0.1287</v>
+        <v>0.1477</v>
       </c>
       <c r="I118" s="9" t="inlineStr">
         <is>
@@ -8904,13 +8902,13 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>70.91</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>41.56</v>
+        <v>40.88</v>
       </c>
       <c r="L118" s="9" t="n">
-        <v>71.62</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="M118" s="9" t="n">
         <v>0.49</v>
@@ -8932,7 +8930,7 @@
       </c>
       <c r="Q118" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -8948,7 +8946,7 @@
         </is>
       </c>
       <c r="C119" s="10" t="n">
-        <v>11.55</v>
+        <v>11.63</v>
       </c>
       <c r="D119" s="10" t="n">
         <v>22.92</v>
@@ -8957,13 +8955,13 @@
         <v>10.97</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>0.0922</v>
+        <v>0.0898</v>
       </c>
       <c r="G119" s="11" t="n">
-        <v>0.1843</v>
+        <v>0.1796</v>
       </c>
       <c r="H119" s="11" t="n">
-        <v>0.3687</v>
+        <v>0.3593</v>
       </c>
       <c r="I119" s="9" t="inlineStr">
         <is>
@@ -8971,13 +8969,13 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>12.83</v>
+        <v>12.92</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="L119" s="9" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="M119" s="9" t="n">
         <v>0.24</v>
@@ -8999,7 +8997,7 @@
       </c>
       <c r="Q119" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -9015,22 +9013,22 @@
         </is>
       </c>
       <c r="C120" s="10" t="n">
-        <v>19.07</v>
+        <v>19.19</v>
       </c>
       <c r="D120" s="10" t="n">
-        <v>21.555</v>
+        <v>21.41</v>
       </c>
       <c r="E120" s="10" t="n">
         <v>15.1</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>0.0191</v>
+        <v>0.0175</v>
       </c>
       <c r="G120" s="11" t="n">
-        <v>0.0383</v>
+        <v>0.0349</v>
       </c>
       <c r="H120" s="11" t="n">
-        <v>0.0766</v>
+        <v>0.0698</v>
       </c>
       <c r="I120" s="9" t="inlineStr">
         <is>
@@ -9038,13 +9036,13 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>11.98</v>
+        <v>11.88</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="L120" s="9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="M120" s="9" t="n">
         <v>0.48</v>
@@ -9066,7 +9064,7 @@
       </c>
       <c r="Q120" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -9082,7 +9080,7 @@
         </is>
       </c>
       <c r="C121" s="6" t="n">
-        <v>9.42</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="D121" s="6" t="n">
         <v>12.015</v>
@@ -9091,13 +9089,13 @@
         <v>8.035</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>0.0559</v>
+        <v>0.0575</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>0.1117</v>
+        <v>0.115</v>
       </c>
       <c r="H121" s="7" t="n">
-        <v>0.2235</v>
+        <v>0.23</v>
       </c>
       <c r="I121" s="5" t="inlineStr">
         <is>
@@ -9105,10 +9103,10 @@
         </is>
       </c>
       <c r="J121" s="5" t="n">
-        <v>11.21</v>
+        <v>11.15</v>
       </c>
       <c r="K121" s="5" t="n">
-        <v>10.61</v>
+        <v>10.55</v>
       </c>
       <c r="L121" s="5" t="n">
         <v>0.5600000000000001</v>
@@ -9133,7 +9131,7 @@
       </c>
       <c r="Q121" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -9149,7 +9147,7 @@
         </is>
       </c>
       <c r="C122" s="10" t="n">
-        <v>22.26</v>
+        <v>22.48</v>
       </c>
       <c r="D122" s="10" t="n">
         <v>25.83</v>
@@ -9158,13 +9156,13 @@
         <v>18.57</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>0.017</v>
+        <v>0.0144</v>
       </c>
       <c r="G122" s="11" t="n">
-        <v>0.034</v>
+        <v>0.0288</v>
       </c>
       <c r="H122" s="11" t="n">
-        <v>0.068</v>
+        <v>0.0575</v>
       </c>
       <c r="I122" s="9" t="inlineStr">
         <is>
@@ -9172,10 +9170,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>11.24</v>
+        <v>11.35</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="L122" s="9" t="inlineStr">
         <is>
@@ -9202,7 +9200,7 @@
       </c>
       <c r="Q122" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -9269,7 +9267,7 @@
       </c>
       <c r="Q123" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -9285,22 +9283,22 @@
         </is>
       </c>
       <c r="C124" s="10" t="n">
-        <v>177.24</v>
+        <v>169.78</v>
       </c>
       <c r="D124" s="10" t="n">
-        <v>252.96</v>
+        <v>247.49</v>
       </c>
       <c r="E124" s="10" t="n">
         <v>131.07</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>0.0227</v>
+        <v>0.0347</v>
       </c>
       <c r="G124" s="11" t="n">
-        <v>0.0455</v>
+        <v>0.0694</v>
       </c>
       <c r="H124" s="11" t="n">
-        <v>0.091</v>
+        <v>0.1389</v>
       </c>
       <c r="I124" s="9" t="inlineStr">
         <is>
@@ -9308,13 +9306,13 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>34.75</v>
+        <v>33.23</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>12.21</v>
+        <v>11.69</v>
       </c>
       <c r="L124" s="9" t="n">
-        <v>11.73</v>
+        <v>11.24</v>
       </c>
       <c r="M124" s="9" t="n">
         <v>3.96</v>
@@ -9336,7 +9334,7 @@
       </c>
       <c r="Q124" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9350,7 @@
         </is>
       </c>
       <c r="C125" s="10" t="n">
-        <v>51.28</v>
+        <v>52.23</v>
       </c>
       <c r="D125" s="10" t="n">
         <v>52.79</v>
@@ -9361,13 +9359,13 @@
         <v>30.39</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>-0.0023</v>
+        <v>-0.0068</v>
       </c>
       <c r="G125" s="11" t="n">
-        <v>-0.0046</v>
+        <v>-0.0136</v>
       </c>
       <c r="H125" s="11" t="n">
-        <v>-0.0091</v>
+        <v>-0.0271</v>
       </c>
       <c r="I125" s="9" t="inlineStr">
         <is>
@@ -9375,13 +9373,13 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>37.71</v>
+        <v>38.4</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="L125" s="9" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="M125" s="9" t="n">
         <v>1.97</v>
@@ -9403,7 +9401,7 @@
       </c>
       <c r="Q125" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9417,7 @@
         </is>
       </c>
       <c r="C126" s="10" t="n">
-        <v>174.81</v>
+        <v>177.51</v>
       </c>
       <c r="D126" s="10" t="n">
         <v>195.84</v>
@@ -9428,13 +9426,13 @@
         <v>112.96</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>-0.012</v>
+        <v>-0.0148</v>
       </c>
       <c r="G126" s="11" t="n">
-        <v>-0.024</v>
+        <v>-0.0296</v>
       </c>
       <c r="H126" s="11" t="n">
-        <v>-0.048</v>
+        <v>-0.0592</v>
       </c>
       <c r="I126" s="9" t="inlineStr">
         <is>
@@ -9442,13 +9440,13 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>17.02</v>
+        <v>17.28</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="L126" s="9" t="n">
-        <v>4.6</v>
+        <v>4.67</v>
       </c>
       <c r="M126" s="9" t="n">
         <v>0.32</v>
@@ -9470,7 +9468,7 @@
       </c>
       <c r="Q126" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -9486,7 +9484,7 @@
         </is>
       </c>
       <c r="C127" s="6" t="n">
-        <v>33.04</v>
+        <v>33.19</v>
       </c>
       <c r="D127" s="6" t="n">
         <v>43.29</v>
@@ -9495,13 +9493,13 @@
         <v>25.5</v>
       </c>
       <c r="F127" s="7" t="n">
-        <v>0.0458</v>
+        <v>0.0455</v>
       </c>
       <c r="G127" s="7" t="n">
-        <v>0.0917</v>
+        <v>0.091</v>
       </c>
       <c r="H127" s="7" t="n">
-        <v>0.1833</v>
+        <v>0.182</v>
       </c>
       <c r="I127" s="5" t="inlineStr">
         <is>
@@ -9509,13 +9507,13 @@
         </is>
       </c>
       <c r="J127" s="5" t="n">
-        <v>22.63</v>
+        <v>22.89</v>
       </c>
       <c r="K127" s="5" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>8.43</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="M127" s="5" t="n">
         <v>0.13</v>
@@ -9537,7 +9535,7 @@
       </c>
       <c r="Q127" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -9553,22 +9551,22 @@
         </is>
       </c>
       <c r="C128" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="D128" s="10" t="n">
         <v>10</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>4.61</v>
+        <v>4.72</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>-0.0116</v>
+        <v>-0.015</v>
       </c>
       <c r="G128" s="11" t="n">
-        <v>-0.0232</v>
+        <v>-0.03</v>
       </c>
       <c r="H128" s="11" t="n">
-        <v>-0.0465</v>
+        <v>-0.0601</v>
       </c>
       <c r="I128" s="9" t="inlineStr">
         <is>
@@ -9576,13 +9574,13 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>8.83</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="L128" s="9" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="M128" s="9" t="n">
         <v>4.66</v>
@@ -9604,7 +9602,7 @@
       </c>
       <c r="Q128" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9618,7 @@
         </is>
       </c>
       <c r="C129" s="10" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="D129" s="10" t="n">
         <v>4.53</v>
@@ -9629,13 +9627,13 @@
         <v>2.86</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>0.0352</v>
+        <v>0.0345</v>
       </c>
       <c r="G129" s="11" t="n">
-        <v>0.0704</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H129" s="11" t="n">
-        <v>0.1408</v>
+        <v>0.138</v>
       </c>
       <c r="I129" s="9" t="inlineStr">
         <is>
@@ -9643,13 +9641,13 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="L129" s="9" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="M129" s="9" t="n">
         <v>0.29</v>
@@ -9671,7 +9669,7 @@
       </c>
       <c r="Q129" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:02</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -9687,7 +9685,7 @@
         </is>
       </c>
       <c r="C130" s="10" t="n">
-        <v>5.16</v>
+        <v>5.24</v>
       </c>
       <c r="D130" s="10" t="n">
         <v>5.29</v>
@@ -9696,13 +9694,13 @@
         <v>2.52</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0081</v>
       </c>
       <c r="G130" s="11" t="n">
-        <v>-0.0167</v>
+        <v>-0.0162</v>
       </c>
       <c r="H130" s="11" t="n">
-        <v>-0.0334</v>
+        <v>-0.0324</v>
       </c>
       <c r="I130" s="9" t="inlineStr">
         <is>
@@ -9710,13 +9708,13 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>15.64</v>
+        <v>15.88</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="L130" s="9" t="n">
-        <v>3.89</v>
+        <v>3.95</v>
       </c>
       <c r="M130" s="9" t="n">
         <v>0.19</v>
@@ -9733,12 +9731,12 @@
       </c>
       <c r="P130" s="12" t="inlineStr">
         <is>
-          <t>South32 Limited operates as a diversified metals and mining company. The company operates through Worsley Alumina, Brazil Alumina, Brazil Aluminium, Hillside Aluminium, Mozal Aluminium, Sierra Gorda, Cannington, Hermosa, Australia Manganese, and South Africa Manganese segments. It has a portfolio of assets producing bauxite, alumina, aluminum, copper, silver, lead, zinc, and manganese products....</t>
+          <t>South32 Limited operates as a diversified metals and mining company. The company operates through Sierra Gorda, Cannington, Hermosa, Australia Manganese, South Africa Manganese, and Mozal Aluminium segments. It explores for copper, silver, lead, zinc, manganese, and base metal deposits. The company has operations in Australia, Bahrain, Brazil, China, Italy, Japan, Mozambique, the Netherlands, S...</t>
         </is>
       </c>
       <c r="Q130" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -9754,7 +9752,7 @@
         </is>
       </c>
       <c r="C131" s="10" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="D131" s="10" t="n">
         <v>4.27</v>
@@ -9763,13 +9761,13 @@
         <v>3.275</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>0.0314</v>
+        <v>0.0322</v>
       </c>
       <c r="G131" s="11" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0643</v>
       </c>
       <c r="H131" s="11" t="n">
-        <v>0.1255</v>
+        <v>0.1286</v>
       </c>
       <c r="I131" s="9" t="inlineStr">
         <is>
@@ -9777,13 +9775,13 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>9.449999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="K131" s="9" t="n">
         <v>0.99</v>
       </c>
       <c r="L131" s="9" t="n">
-        <v>7.28</v>
+        <v>7.27</v>
       </c>
       <c r="M131" s="9" t="n">
         <v>0.72</v>
@@ -9805,7 +9803,7 @@
       </c>
       <c r="Q131" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -9821,7 +9819,7 @@
         </is>
       </c>
       <c r="C132" s="10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="D132" s="10" t="n">
         <v>8.699999999999999</v>
@@ -9849,10 +9847,10 @@
         </is>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="L132" s="9" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="M132" s="9" t="n">
         <v>1.69</v>
@@ -9874,7 +9872,7 @@
       </c>
       <c r="Q132" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -9941,7 +9939,7 @@
       </c>
       <c r="Q133" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -9957,7 +9955,7 @@
         </is>
       </c>
       <c r="C134" s="6" t="n">
-        <v>14.69</v>
+        <v>14.32</v>
       </c>
       <c r="D134" s="6" t="n">
         <v>29.84</v>
@@ -9966,13 +9964,13 @@
         <v>11.745</v>
       </c>
       <c r="F134" s="7" t="n">
-        <v>0.0789</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="G134" s="7" t="n">
-        <v>0.1578</v>
+        <v>0.1748</v>
       </c>
       <c r="H134" s="7" t="n">
-        <v>0.3155</v>
+        <v>0.3495</v>
       </c>
       <c r="I134" s="5" t="inlineStr">
         <is>
@@ -9980,13 +9978,13 @@
         </is>
       </c>
       <c r="J134" s="5" t="n">
-        <v>20.66</v>
+        <v>20.13</v>
       </c>
       <c r="K134" s="5" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="L134" s="5" t="n">
-        <v>4.09</v>
+        <v>3.99</v>
       </c>
       <c r="M134" s="5" t="n">
         <v>0.6</v>
@@ -10008,7 +10006,7 @@
       </c>
       <c r="Q134" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -10024,7 +10022,7 @@
         </is>
       </c>
       <c r="C135" s="10" t="n">
-        <v>24.34</v>
+        <v>24.71</v>
       </c>
       <c r="D135" s="10" t="n">
         <v>31.81</v>
@@ -10033,13 +10031,13 @@
         <v>13.04</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>0.0298</v>
+        <v>0.0256</v>
       </c>
       <c r="G135" s="11" t="n">
-        <v>0.0597</v>
+        <v>0.0513</v>
       </c>
       <c r="H135" s="11" t="n">
-        <v>0.1193</v>
+        <v>0.1025</v>
       </c>
       <c r="I135" s="9" t="inlineStr">
         <is>
@@ -10047,10 +10045,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>19.47</v>
+        <v>19.77</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="L135" s="9" t="n">
         <v>0.59</v>
@@ -10075,7 +10073,7 @@
       </c>
       <c r="Q135" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -10091,7 +10089,7 @@
         </is>
       </c>
       <c r="C136" s="6" t="n">
-        <v>4.36</v>
+        <v>4.46</v>
       </c>
       <c r="D136" s="6" t="n">
         <v>6.75</v>
@@ -10100,13 +10098,13 @@
         <v>3.71</v>
       </c>
       <c r="F136" s="7" t="n">
-        <v>0.0486</v>
+        <v>0.0419</v>
       </c>
       <c r="G136" s="7" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0838</v>
       </c>
       <c r="H136" s="7" t="n">
-        <v>0.1944</v>
+        <v>0.1677</v>
       </c>
       <c r="I136" s="5" t="inlineStr">
         <is>
@@ -10114,13 +10112,13 @@
         </is>
       </c>
       <c r="J136" s="5" t="n">
-        <v>10.63</v>
+        <v>10.88</v>
       </c>
       <c r="K136" s="5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="M136" s="5" t="n">
         <v>0.47</v>
@@ -10142,7 +10140,7 @@
       </c>
       <c r="Q136" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10156,7 @@
         </is>
       </c>
       <c r="C137" s="10" t="n">
-        <v>0.13</v>
+        <v>0.125</v>
       </c>
       <c r="D137" s="10" t="n">
         <v>0.195</v>
@@ -10167,13 +10165,13 @@
         <v>0.083</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="G137" s="11" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="H137" s="11" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I137" s="9" t="inlineStr">
         <is>
@@ -10181,13 +10179,13 @@
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>-50.19</v>
+        <v>-11.39</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="L137" s="9" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="M137" s="9" t="n">
         <v>0.65</v>
@@ -10209,7 +10207,7 @@
       </c>
       <c r="Q137" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -10225,7 +10223,7 @@
         </is>
       </c>
       <c r="C138" s="10" t="n">
-        <v>19.59</v>
+        <v>19.64</v>
       </c>
       <c r="D138" s="10" t="n">
         <v>24.27</v>
@@ -10234,13 +10232,13 @@
         <v>18.26</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>0.0373</v>
+        <v>0.0366</v>
       </c>
       <c r="G138" s="11" t="n">
-        <v>0.0746</v>
+        <v>0.0731</v>
       </c>
       <c r="H138" s="11" t="n">
-        <v>0.1492</v>
+        <v>0.1463</v>
       </c>
       <c r="I138" s="9" t="inlineStr">
         <is>
@@ -10248,7 +10246,7 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>15.93</v>
+        <v>15.97</v>
       </c>
       <c r="K138" s="9" t="n">
         <v>1.16</v>
@@ -10276,7 +10274,7 @@
       </c>
       <c r="Q138" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -10351,7 +10349,7 @@
       </c>
       <c r="Q139" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -10367,7 +10365,7 @@
         </is>
       </c>
       <c r="C140" s="10" t="n">
-        <v>44.48</v>
+        <v>44.46</v>
       </c>
       <c r="D140" s="10" t="n">
         <v>47.16</v>
@@ -10376,13 +10374,13 @@
         <v>34.78</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>-0.0242</v>
+        <v>-0.0241</v>
       </c>
       <c r="G140" s="11" t="n">
-        <v>-0.0484</v>
+        <v>-0.0482</v>
       </c>
       <c r="H140" s="11" t="n">
-        <v>-0.0968</v>
+        <v>-0.0964</v>
       </c>
       <c r="I140" s="9" t="inlineStr">
         <is>
@@ -10396,7 +10394,7 @@
         <v>1.26</v>
       </c>
       <c r="L140" s="9" t="n">
-        <v>5.96</v>
+        <v>5.95</v>
       </c>
       <c r="M140" s="9" t="n">
         <v>9.59</v>
@@ -10418,7 +10416,7 @@
       </c>
       <c r="Q140" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -10434,7 +10432,7 @@
         </is>
       </c>
       <c r="C141" s="6" t="n">
-        <v>8.140000000000001</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="D141" s="6" t="n">
         <v>8.640000000000001</v>
@@ -10443,13 +10441,13 @@
         <v>5.9</v>
       </c>
       <c r="F141" s="7" t="n">
-        <v>0.0222</v>
+        <v>0.0186</v>
       </c>
       <c r="G141" s="7" t="n">
-        <v>0.0445</v>
+        <v>0.0371</v>
       </c>
       <c r="H141" s="7" t="n">
-        <v>0.089</v>
+        <v>0.0743</v>
       </c>
       <c r="I141" s="5" t="inlineStr">
         <is>
@@ -10457,10 +10455,10 @@
         </is>
       </c>
       <c r="J141" s="5" t="n">
-        <v>26.26</v>
+        <v>26.71</v>
       </c>
       <c r="K141" s="5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
@@ -10487,7 +10485,7 @@
       </c>
       <c r="Q141" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -10503,22 +10501,22 @@
         </is>
       </c>
       <c r="C142" s="10" t="n">
-        <v>13.45</v>
+        <v>13.15</v>
       </c>
       <c r="D142" s="10" t="n">
-        <v>18.865</v>
+        <v>18.84</v>
       </c>
       <c r="E142" s="10" t="n">
         <v>10.08</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>0.0242</v>
+        <v>0.0305</v>
       </c>
       <c r="G142" s="11" t="n">
-        <v>0.0484</v>
+        <v>0.0609</v>
       </c>
       <c r="H142" s="11" t="n">
-        <v>0.0969</v>
+        <v>0.1219</v>
       </c>
       <c r="I142" s="9" t="inlineStr">
         <is>
@@ -10526,13 +10524,13 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>14.78</v>
+        <v>14.45</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="L142" s="9" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="M142" s="9" t="n">
         <v>1.02</v>
@@ -10554,7 +10552,7 @@
       </c>
       <c r="Q142" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -10570,22 +10568,22 @@
         </is>
       </c>
       <c r="C143" s="10" t="n">
-        <v>18.86</v>
+        <v>18.85</v>
       </c>
       <c r="D143" s="10" t="n">
-        <v>21.48</v>
+        <v>21.43</v>
       </c>
       <c r="E143" s="10" t="n">
         <v>13.8</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>0.011</v>
+        <v>0.0111</v>
       </c>
       <c r="G143" s="11" t="n">
-        <v>0.0219</v>
+        <v>0.0222</v>
       </c>
       <c r="H143" s="11" t="n">
-        <v>0.0439</v>
+        <v>0.0444</v>
       </c>
       <c r="I143" s="9" t="inlineStr">
         <is>
@@ -10593,7 +10591,7 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>19.85</v>
+        <v>19.84</v>
       </c>
       <c r="K143" s="9" t="n">
         <v>1.93</v>
@@ -10621,7 +10619,7 @@
       </c>
       <c r="Q143" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -10696,7 +10694,7 @@
       </c>
       <c r="Q144" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10710,7 @@
         </is>
       </c>
       <c r="C145" s="10" t="n">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="D145" s="10" t="n">
         <v>1.19</v>
@@ -10721,13 +10719,13 @@
         <v>0.66</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>0.0303</v>
+        <v>0.024</v>
       </c>
       <c r="G145" s="11" t="n">
-        <v>0.0605</v>
+        <v>0.0481</v>
       </c>
       <c r="H145" s="11" t="n">
-        <v>0.121</v>
+        <v>0.0961</v>
       </c>
       <c r="I145" s="9" t="inlineStr">
         <is>
@@ -10735,13 +10733,13 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="L145" s="9" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="M145" s="9" t="n">
         <v>0.66</v>
@@ -10763,7 +10761,7 @@
       </c>
       <c r="Q145" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10777,7 @@
         </is>
       </c>
       <c r="C146" s="10" t="n">
-        <v>14.3</v>
+        <v>13.96</v>
       </c>
       <c r="D146" s="10" t="n">
         <v>15.62</v>
@@ -10788,13 +10786,13 @@
         <v>13.25</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>-0.0077</v>
+        <v>-0.0018</v>
       </c>
       <c r="G146" s="11" t="n">
-        <v>-0.0154</v>
+        <v>-0.0036</v>
       </c>
       <c r="H146" s="11" t="n">
-        <v>-0.0308</v>
+        <v>-0.0072</v>
       </c>
       <c r="I146" s="9" t="inlineStr">
         <is>
@@ -10802,10 +10800,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>119.17</v>
+        <v>116.33</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>5.07</v>
+        <v>4.95</v>
       </c>
       <c r="L146" s="9" t="inlineStr">
         <is>
@@ -10832,7 +10830,7 @@
       </c>
       <c r="Q146" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10846,7 @@
         </is>
       </c>
       <c r="C147" s="10" t="n">
-        <v>4.67</v>
+        <v>4.63</v>
       </c>
       <c r="D147" s="10" t="n">
         <v>5.58</v>
@@ -10857,13 +10855,13 @@
         <v>4.56</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>0.0183</v>
+        <v>0.0206</v>
       </c>
       <c r="G147" s="11" t="n">
-        <v>0.0366</v>
+        <v>0.0412</v>
       </c>
       <c r="H147" s="11" t="n">
-        <v>0.0732</v>
+        <v>0.0825</v>
       </c>
       <c r="I147" s="9" t="inlineStr">
         <is>
@@ -10871,10 +10869,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>23.35</v>
+        <v>23.15</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>4.13</v>
+        <v>4.1</v>
       </c>
       <c r="L147" s="9" t="inlineStr">
         <is>
@@ -10901,7 +10899,7 @@
       </c>
       <c r="Q147" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -10917,7 +10915,7 @@
         </is>
       </c>
       <c r="C148" s="10" t="n">
-        <v>32.59</v>
+        <v>32.19</v>
       </c>
       <c r="D148" s="10" t="n">
         <v>39.99</v>
@@ -10926,13 +10924,13 @@
         <v>20.14</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>-0.011</v>
+        <v>-0.008</v>
       </c>
       <c r="G148" s="11" t="n">
-        <v>-0.0219</v>
+        <v>-0.016</v>
       </c>
       <c r="H148" s="11" t="n">
-        <v>-0.0439</v>
+        <v>-0.032</v>
       </c>
       <c r="I148" s="9" t="inlineStr">
         <is>
@@ -10940,13 +10938,13 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>75.79000000000001</v>
+        <v>74.86</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>24.88</v>
+        <v>24.57</v>
       </c>
       <c r="L148" s="9" t="n">
-        <v>16.9</v>
+        <v>16.69</v>
       </c>
       <c r="M148" s="9" t="n">
         <v>0.12</v>
@@ -10968,7 +10966,7 @@
       </c>
       <c r="Q148" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -10984,7 +10982,7 @@
         </is>
       </c>
       <c r="C149" s="10" t="n">
-        <v>3.77</v>
+        <v>3.79</v>
       </c>
       <c r="D149" s="10" t="n">
         <v>5.85</v>
@@ -10993,13 +10991,13 @@
         <v>3.47</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>0.0214</v>
+        <v>0.02</v>
       </c>
       <c r="G149" s="11" t="n">
-        <v>0.0428</v>
+        <v>0.0399</v>
       </c>
       <c r="H149" s="11" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.0798</v>
       </c>
       <c r="I149" s="9" t="inlineStr">
         <is>
@@ -11007,13 +11005,13 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>125.67</v>
+        <v>126.33</v>
       </c>
       <c r="K149" s="9" t="n">
         <v>0.85</v>
       </c>
       <c r="L149" s="9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M149" s="9" t="n">
         <v>0.49</v>
@@ -11035,7 +11033,7 @@
       </c>
       <c r="Q149" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11049,7 @@
         </is>
       </c>
       <c r="C150" s="10" t="n">
-        <v>5.48</v>
+        <v>5.54</v>
       </c>
       <c r="D150" s="10" t="n">
         <v>7.94</v>
@@ -11060,13 +11058,13 @@
         <v>3.34</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>0.0367</v>
+        <v>0.0336</v>
       </c>
       <c r="G150" s="11" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.0672</v>
       </c>
       <c r="H150" s="11" t="n">
-        <v>0.1469</v>
+        <v>0.1345</v>
       </c>
       <c r="I150" s="9" t="inlineStr">
         <is>
@@ -11074,13 +11072,13 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>13.24</v>
+        <v>13.39</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="L150" s="9" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="M150" s="9" t="n">
         <v>0.6</v>
@@ -11102,7 +11100,7 @@
       </c>
       <c r="Q150" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -11118,7 +11116,7 @@
         </is>
       </c>
       <c r="C151" s="10" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="D151" s="10" t="n">
         <v>2.73</v>
@@ -11127,13 +11125,13 @@
         <v>2.22</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>0.0123</v>
+        <v>0.0112</v>
       </c>
       <c r="G151" s="11" t="n">
-        <v>0.0246</v>
+        <v>0.0225</v>
       </c>
       <c r="H151" s="11" t="n">
-        <v>0.0492</v>
+        <v>0.045</v>
       </c>
       <c r="I151" s="9" t="inlineStr">
         <is>
@@ -11141,13 +11139,13 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>8.300000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="L151" s="9" t="n">
-        <v>8.18</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M151" s="9" t="n">
         <v>0.41</v>
@@ -11169,7 +11167,7 @@
       </c>
       <c r="Q151" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -11185,22 +11183,22 @@
         </is>
       </c>
       <c r="C152" s="6" t="n">
-        <v>2.96</v>
+        <v>3.04</v>
       </c>
       <c r="D152" s="6" t="n">
-        <v>2.96</v>
+        <v>3.04</v>
       </c>
       <c r="E152" s="6" t="n">
         <v>1.695</v>
       </c>
       <c r="F152" s="7" t="n">
-        <v>0.0018</v>
+        <v>-0.0048</v>
       </c>
       <c r="G152" s="7" t="n">
-        <v>0.0036</v>
+        <v>-0.0097</v>
       </c>
       <c r="H152" s="7" t="n">
-        <v>0.0071</v>
+        <v>-0.0194</v>
       </c>
       <c r="I152" s="5" t="inlineStr">
         <is>
@@ -11208,13 +11206,13 @@
         </is>
       </c>
       <c r="J152" s="5" t="n">
-        <v>22.77</v>
+        <v>23.38</v>
       </c>
       <c r="K152" s="5" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="M152" s="5" t="n">
         <v>3.01</v>
@@ -11236,7 +11234,7 @@
       </c>
       <c r="Q152" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -11252,7 +11250,7 @@
         </is>
       </c>
       <c r="C153" s="10" t="n">
-        <v>34.55</v>
+        <v>34.36</v>
       </c>
       <c r="D153" s="10" t="n">
         <v>43.32</v>
@@ -11261,13 +11259,13 @@
         <v>33.46</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>-0.0076</v>
+        <v>-0.0063</v>
       </c>
       <c r="G153" s="11" t="n">
-        <v>-0.0153</v>
+        <v>-0.0126</v>
       </c>
       <c r="H153" s="11" t="n">
-        <v>-0.0305</v>
+        <v>-0.0252</v>
       </c>
       <c r="I153" s="9" t="inlineStr">
         <is>
@@ -11275,13 +11273,13 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>17.02</v>
+        <v>16.93</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="L153" s="9" t="n">
-        <v>5.3</v>
+        <v>5.27</v>
       </c>
       <c r="M153" s="9" t="inlineStr">
         <is>
@@ -11305,7 +11303,7 @@
       </c>
       <c r="Q153" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -11321,7 +11319,7 @@
         </is>
       </c>
       <c r="C154" s="6" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="D154" s="6" t="n">
         <v>5.04</v>
@@ -11330,13 +11328,13 @@
         <v>2.17</v>
       </c>
       <c r="F154" s="7" t="n">
-        <v>0.0523</v>
+        <v>0.0465</v>
       </c>
       <c r="G154" s="7" t="n">
-        <v>0.1046</v>
+        <v>0.093</v>
       </c>
       <c r="H154" s="7" t="n">
-        <v>0.2092</v>
+        <v>0.1861</v>
       </c>
       <c r="I154" s="5" t="inlineStr">
         <is>
@@ -11344,13 +11342,13 @@
         </is>
       </c>
       <c r="J154" s="5" t="n">
-        <v>38</v>
+        <v>38.8</v>
       </c>
       <c r="K154" s="5" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="L154" s="5" t="n">
-        <v>3.49</v>
+        <v>3.56</v>
       </c>
       <c r="M154" s="5" t="n">
         <v>0.44</v>
@@ -11372,7 +11370,7 @@
       </c>
       <c r="Q154" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -11388,7 +11386,7 @@
         </is>
       </c>
       <c r="C155" s="10" t="n">
-        <v>79.44</v>
+        <v>77.08</v>
       </c>
       <c r="D155" s="10" t="n">
         <v>94.7</v>
@@ -11397,13 +11395,13 @@
         <v>70.8</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>-0.0074</v>
+        <v>0</v>
       </c>
       <c r="G155" s="11" t="n">
-        <v>-0.0148</v>
+        <v>0.0001</v>
       </c>
       <c r="H155" s="11" t="n">
-        <v>-0.0296</v>
+        <v>0.0001</v>
       </c>
       <c r="I155" s="9" t="inlineStr">
         <is>
@@ -11411,13 +11409,13 @@
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>31.4</v>
+        <v>30.35</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>11.48</v>
+        <v>11.14</v>
       </c>
       <c r="L155" s="9" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="M155" s="9" t="n">
         <v>1.59</v>
@@ -11439,7 +11437,7 @@
       </c>
       <c r="Q155" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -11455,7 +11453,7 @@
         </is>
       </c>
       <c r="C156" s="10" t="n">
-        <v>8.550000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="D156" s="10" t="n">
         <v>9.9</v>
@@ -11464,13 +11462,13 @@
         <v>5.94</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>-0.0083</v>
+        <v>-0.011</v>
       </c>
       <c r="G156" s="11" t="n">
-        <v>-0.0165</v>
+        <v>-0.0221</v>
       </c>
       <c r="H156" s="11" t="n">
-        <v>-0.033</v>
+        <v>-0.0442</v>
       </c>
       <c r="I156" s="9" t="inlineStr">
         <is>
@@ -11478,13 +11476,13 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>17.81</v>
+        <v>18.02</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="L156" s="9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="M156" s="9" t="n">
         <v>0.39</v>
@@ -11506,7 +11504,7 @@
       </c>
       <c r="Q156" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -11522,7 +11520,7 @@
         </is>
       </c>
       <c r="C157" s="10" t="n">
-        <v>10.22</v>
+        <v>10.02</v>
       </c>
       <c r="D157" s="10" t="n">
         <v>14.85</v>
@@ -11531,13 +11529,13 @@
         <v>9.609999999999999</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>0.0355</v>
+        <v>0.0412</v>
       </c>
       <c r="G157" s="11" t="n">
-        <v>0.0709</v>
+        <v>0.0823</v>
       </c>
       <c r="H157" s="11" t="n">
-        <v>0.1419</v>
+        <v>0.1647</v>
       </c>
       <c r="I157" s="9" t="inlineStr">
         <is>
@@ -11545,7 +11543,7 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>21.74</v>
+        <v>21.32</v>
       </c>
       <c r="K157" s="9" t="inlineStr">
         <is>
@@ -11553,7 +11551,7 @@
         </is>
       </c>
       <c r="L157" s="9" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="M157" s="9" t="n">
         <v>0.58</v>
@@ -11575,7 +11573,7 @@
       </c>
       <c r="Q157" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -11591,7 +11589,7 @@
         </is>
       </c>
       <c r="C158" s="10" t="n">
-        <v>40.31</v>
+        <v>39.33</v>
       </c>
       <c r="D158" s="10" t="n">
         <v>41.19</v>
@@ -11600,13 +11598,13 @@
         <v>25.51</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>-0.0059</v>
+        <v>0.0001</v>
       </c>
       <c r="G158" s="11" t="n">
-        <v>-0.0119</v>
+        <v>0.0003</v>
       </c>
       <c r="H158" s="11" t="n">
-        <v>-0.0237</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="I158" s="9" t="inlineStr">
         <is>
@@ -11614,10 +11612,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>43.82</v>
+        <v>42.75</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>10.62</v>
+        <v>10</v>
       </c>
       <c r="L158" s="9" t="inlineStr">
         <is>
@@ -11644,7 +11642,7 @@
       </c>
       <c r="Q158" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -11660,7 +11658,7 @@
         </is>
       </c>
       <c r="C159" s="10" t="n">
-        <v>32.42</v>
+        <v>32.7</v>
       </c>
       <c r="D159" s="10" t="n">
         <v>35.82</v>
@@ -11669,13 +11667,13 @@
         <v>21.96</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>0.0054</v>
+        <v>0.0041</v>
       </c>
       <c r="G159" s="11" t="n">
-        <v>0.0108</v>
+        <v>0.0083</v>
       </c>
       <c r="H159" s="11" t="n">
-        <v>0.0216</v>
+        <v>0.0165</v>
       </c>
       <c r="I159" s="9" t="inlineStr">
         <is>
@@ -11683,13 +11681,13 @@
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>14.47</v>
+        <v>14.6</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="L159" s="9" t="n">
-        <v>4.45</v>
+        <v>4.49</v>
       </c>
       <c r="M159" s="9" t="n">
         <v>0.33</v>
@@ -11711,7 +11709,7 @@
       </c>
       <c r="Q159" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -11727,7 +11725,7 @@
         </is>
       </c>
       <c r="C160" s="10" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="D160" s="10" t="n">
         <v>2.82</v>
@@ -11736,13 +11734,13 @@
         <v>2.29</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>0.0328</v>
+        <v>0.0316</v>
       </c>
       <c r="G160" s="11" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.0633</v>
       </c>
       <c r="H160" s="11" t="n">
-        <v>0.1313</v>
+        <v>0.1265</v>
       </c>
       <c r="I160" s="9" t="inlineStr">
         <is>
@@ -11750,13 +11748,13 @@
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>11.75</v>
+        <v>11.8</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>146.87</v>
+        <v>147.5</v>
       </c>
       <c r="L160" s="9" t="n">
-        <v>19.16</v>
+        <v>19.24</v>
       </c>
       <c r="M160" s="9" t="n">
         <v>0.49</v>
@@ -11778,7 +11776,7 @@
       </c>
       <c r="Q160" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -11794,22 +11792,22 @@
         </is>
       </c>
       <c r="C161" s="6" t="n">
-        <v>40.38</v>
+        <v>39.7</v>
       </c>
       <c r="D161" s="6" t="n">
-        <v>100.23</v>
+        <v>99.7</v>
       </c>
       <c r="E161" s="6" t="n">
         <v>28.76</v>
       </c>
       <c r="F161" s="7" t="n">
-        <v>0.1329</v>
+        <v>0.1408</v>
       </c>
       <c r="G161" s="7" t="n">
-        <v>0.2658</v>
+        <v>0.2816</v>
       </c>
       <c r="H161" s="7" t="n">
-        <v>0.5316</v>
+        <v>0.5632</v>
       </c>
       <c r="I161" s="5" t="inlineStr">
         <is>
@@ -11817,13 +11815,13 @@
         </is>
       </c>
       <c r="J161" s="5" t="n">
-        <v>54.57</v>
+        <v>53.65</v>
       </c>
       <c r="K161" s="5" t="n">
-        <v>5.16</v>
+        <v>5.07</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>9.73</v>
+        <v>9.56</v>
       </c>
       <c r="M161" s="5" t="n">
         <v>1.15</v>
@@ -11845,7 +11843,7 @@
       </c>
       <c r="Q161" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -11861,7 +11859,7 @@
         </is>
       </c>
       <c r="C162" s="6" t="n">
-        <v>82.87</v>
+        <v>83.28</v>
       </c>
       <c r="D162" s="6" t="n">
         <v>166</v>
@@ -11870,13 +11868,13 @@
         <v>61.45</v>
       </c>
       <c r="F162" s="7" t="n">
-        <v>0.1276</v>
+        <v>0.1252</v>
       </c>
       <c r="G162" s="7" t="n">
-        <v>0.2552</v>
+        <v>0.2504</v>
       </c>
       <c r="H162" s="7" t="n">
-        <v>0.5104</v>
+        <v>0.5008</v>
       </c>
       <c r="I162" s="5" t="inlineStr">
         <is>
@@ -11884,13 +11882,13 @@
         </is>
       </c>
       <c r="J162" s="5" t="n">
-        <v>42.26</v>
+        <v>42.47</v>
       </c>
       <c r="K162" s="5" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="L162" s="5" t="n">
-        <v>5.32</v>
+        <v>5.34</v>
       </c>
       <c r="M162" s="5" t="n">
         <v>0.39</v>
@@ -11912,7 +11910,7 @@
       </c>
       <c r="Q162" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -11928,7 +11926,7 @@
         </is>
       </c>
       <c r="C163" s="6" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="D163" s="6" t="n">
         <v>4.93</v>
@@ -11937,13 +11935,13 @@
         <v>1.375</v>
       </c>
       <c r="F163" s="7" t="n">
-        <v>0.1798</v>
+        <v>0.1609</v>
       </c>
       <c r="G163" s="7" t="n">
-        <v>0.3596</v>
+        <v>0.3218</v>
       </c>
       <c r="H163" s="7" t="n">
-        <v>0.7192</v>
+        <v>0.6437</v>
       </c>
       <c r="I163" s="5" t="inlineStr">
         <is>
@@ -11951,13 +11949,13 @@
         </is>
       </c>
       <c r="J163" s="5" t="n">
-        <v>27.78</v>
+        <v>29.11</v>
       </c>
       <c r="K163" s="5" t="n">
-        <v>4.78</v>
+        <v>5.01</v>
       </c>
       <c r="L163" s="5" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="M163" s="5" t="n">
         <v>4.09</v>
@@ -11979,7 +11977,7 @@
       </c>
       <c r="Q163" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -12169,7 +12167,7 @@
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -12244,7 +12242,7 @@
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -12260,7 +12258,7 @@
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>1.225</v>
+        <v>1.305</v>
       </c>
       <c r="D4" s="10" t="n">
         <v>2.65</v>
@@ -12269,13 +12267,13 @@
         <v>0.76</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>0.0487</v>
+        <v>0.0321</v>
       </c>
       <c r="G4" s="11" t="n">
-        <v>0.0974</v>
+        <v>0.0643</v>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0.1948</v>
+        <v>0.1285</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
@@ -12283,16 +12281,16 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>8.5</v>
+        <v>12.74</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>4.71</v>
+        <v>5.02</v>
       </c>
       <c r="L4" s="9" t="n">
-        <v>9.619999999999999</v>
+        <v>6.49</v>
       </c>
       <c r="M4" s="9" t="n">
-        <v>1.28</v>
+        <v>0.34</v>
       </c>
       <c r="N4" s="12" t="inlineStr">
         <is>
@@ -12311,7 +12309,7 @@
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -12327,7 +12325,7 @@
         </is>
       </c>
       <c r="C5" s="10" t="n">
-        <v>0.046</v>
+        <v>0.047</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>0.16</v>
@@ -12355,10 +12353,10 @@
         </is>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>63.68</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="M5" s="9" t="n">
         <v>0.62</v>
@@ -12380,7 +12378,7 @@
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -12405,13 +12403,13 @@
         <v>0.113</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>1.9672</v>
+        <v>1.9748</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>3.9343</v>
+        <v>3.9496</v>
       </c>
       <c r="H6" s="11" t="n">
-        <v>7.8686</v>
+        <v>7.8992</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -12419,10 +12417,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>-11.64</v>
+        <v>-11.63</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>11.67</v>
+        <v>10.34</v>
       </c>
       <c r="L6" s="9" t="n">
         <v>150.41</v>
@@ -12447,7 +12445,7 @@
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12467,7 @@
         <v>0.46</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.068</v>
+        <v>0.066</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>0.8774999999999999</v>
@@ -12514,7 +12512,7 @@
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -12530,22 +12528,22 @@
         </is>
       </c>
       <c r="C8" s="10" t="n">
-        <v>6.48</v>
+        <v>6.61</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>6.8</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>3.87</v>
+        <v>4.015</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>-0.005</v>
+        <v>-0.0098</v>
       </c>
       <c r="G8" s="11" t="n">
-        <v>-0.01</v>
+        <v>-0.0197</v>
       </c>
       <c r="H8" s="11" t="n">
-        <v>-0.0201</v>
+        <v>-0.0393</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
@@ -12553,13 +12551,13 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>14.73</v>
+        <v>15.02</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>5.8</v>
+        <v>5.91</v>
       </c>
       <c r="M8" s="9" t="n">
         <v>0.09</v>
@@ -12581,7 +12579,7 @@
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:46</t>
         </is>
       </c>
     </row>
@@ -12603,7 +12601,7 @@
         <v>0.892</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.352</v>
+        <v>0.355</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>0.0682</v>
@@ -12626,7 +12624,7 @@
         <v>2.14</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>256.98</v>
+        <v>260.43</v>
       </c>
       <c r="M9" s="5" t="n">
         <v>0.21</v>
@@ -12648,7 +12646,7 @@
       </c>
       <c r="Q9" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12662,7 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>15.36</v>
+        <v>15.27</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>18.32</v>
@@ -12673,13 +12671,13 @@
         <v>8.26</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0.1314</v>
+        <v>0.1337</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>0.2629</v>
+        <v>0.2674</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>0.5258</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
@@ -12687,13 +12685,13 @@
         </is>
       </c>
       <c r="J10" s="5" t="n">
-        <v>109.71</v>
+        <v>109.07</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>8.640000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>5.86</v>
+        <v>5.82</v>
       </c>
       <c r="M10" s="5" t="n">
         <v>1.19</v>
@@ -12715,7 +12713,7 @@
       </c>
       <c r="Q10" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12729,7 @@
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>0.225</v>
+        <v>0.245</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>0.49</v>
@@ -12740,13 +12738,13 @@
         <v>0.145</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>-0.0375</v>
+        <v>-0.0542</v>
       </c>
       <c r="G11" s="11" t="n">
-        <v>-0.075</v>
+        <v>-0.1084</v>
       </c>
       <c r="H11" s="11" t="n">
-        <v>-0.1501</v>
+        <v>-0.2168</v>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
@@ -12754,13 +12752,13 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>4.21</v>
+        <v>4.59</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="M11" s="9" t="n">
         <v>3.69</v>
@@ -12782,7 +12780,7 @@
       </c>
       <c r="Q11" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -12807,13 +12805,13 @@
         <v>7.45</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>0.0258</v>
+        <v>0.0262</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>0.0516</v>
+        <v>0.0524</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>0.1033</v>
+        <v>0.1047</v>
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
@@ -12849,7 +12847,7 @@
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12863,7 @@
         </is>
       </c>
       <c r="C13" s="10" t="n">
-        <v>22.94</v>
+        <v>23.07</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>25</v>
@@ -12874,13 +12872,13 @@
         <v>12.02</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0053</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>-0.0013</v>
+        <v>-0.0106</v>
       </c>
       <c r="H13" s="11" t="n">
-        <v>-0.0025</v>
+        <v>-0.0211</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
@@ -12888,13 +12886,13 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>21.44</v>
+        <v>21.56</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>3.94</v>
+        <v>3.96</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>6.5</v>
+        <v>6.54</v>
       </c>
       <c r="M13" s="9" t="n">
         <v>1.65</v>
@@ -12916,7 +12914,7 @@
       </c>
       <c r="Q13" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -12932,7 +12930,7 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>0.735</v>
+        <v>0.73</v>
       </c>
       <c r="D14" s="10" t="n">
         <v>1.295</v>
@@ -12941,13 +12939,13 @@
         <v>0.665</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>0.1304</v>
+        <v>0.1331</v>
       </c>
       <c r="G14" s="11" t="n">
-        <v>0.2609</v>
+        <v>0.2661</v>
       </c>
       <c r="H14" s="11" t="n">
-        <v>0.5218</v>
+        <v>0.5322</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
@@ -12955,10 +12953,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>18.38</v>
+        <v>18.25</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="L14" s="9" t="n">
         <v>0.8</v>
@@ -12983,7 +12981,7 @@
       </c>
       <c r="Q14" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -12999,7 +12997,7 @@
         </is>
       </c>
       <c r="C15" s="10" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>1.315</v>
@@ -13008,13 +13006,13 @@
         <v>0.755</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>0.0486</v>
+        <v>0.0453</v>
       </c>
       <c r="G15" s="11" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0907</v>
       </c>
       <c r="H15" s="11" t="n">
-        <v>0.1944</v>
+        <v>0.1813</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
@@ -13022,13 +13020,13 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>-491.8</v>
+        <v>-497.27</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>-18</v>
+        <v>-18.2</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
@@ -13052,7 +13050,7 @@
       </c>
       <c r="Q15" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -13094,7 +13092,7 @@
         <v>2.45</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="L16" s="9" t="n">
         <v>0.14</v>
@@ -13119,7 +13117,7 @@
       </c>
       <c r="Q16" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -13135,7 +13133,7 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>1.32</v>
+        <v>1.315</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>2.75</v>
@@ -13144,13 +13142,13 @@
         <v>1.05</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>0.1903</v>
+        <v>0.192</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>0.3807</v>
+        <v>0.384</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>0.7614</v>
+        <v>0.7681</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
@@ -13158,13 +13156,13 @@
         </is>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-30.69</v>
+        <v>-30.57</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>4.19</v>
+        <v>4.17</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-1300.54</v>
+        <v>-1295.62</v>
       </c>
       <c r="M17" s="5" t="n">
         <v>1.45</v>
@@ -13186,7 +13184,7 @@
       </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -13261,7 +13259,7 @@
       </c>
       <c r="Q18" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -13277,22 +13275,22 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>0.8</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>0.225</v>
+        <v>0.235</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>0.1607</v>
+        <v>0.1438</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0.3214</v>
+        <v>0.2877</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0.6429</v>
+        <v>0.5753</v>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
@@ -13300,13 +13298,13 @@
         </is>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-21.21</v>
+        <v>-22.12</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>79.95</v>
+        <v>83.38</v>
       </c>
       <c r="M19" s="5" t="n">
         <v>0.77</v>
@@ -13328,7 +13326,7 @@
       </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -13344,7 +13342,7 @@
         </is>
       </c>
       <c r="C20" s="10" t="n">
-        <v>1.64</v>
+        <v>1.635</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>2.97</v>
@@ -13353,13 +13351,13 @@
         <v>1.215</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>0.0431</v>
+        <v>0.044</v>
       </c>
       <c r="G20" s="11" t="n">
-        <v>0.0863</v>
+        <v>0.0881</v>
       </c>
       <c r="H20" s="11" t="n">
-        <v>0.1726</v>
+        <v>0.1761</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -13372,10 +13370,10 @@
         </is>
       </c>
       <c r="K20" s="9" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>-699.91</v>
+        <v>-697.78</v>
       </c>
       <c r="M20" s="9" t="n">
         <v>0.51</v>
@@ -13397,7 +13395,7 @@
       </c>
       <c r="Q20" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -13413,7 +13411,7 @@
         </is>
       </c>
       <c r="C21" s="10" t="n">
-        <v>1.42</v>
+        <v>1.465</v>
       </c>
       <c r="D21" s="10" t="n">
         <v>2.2</v>
@@ -13422,13 +13420,13 @@
         <v>0.995</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>0.019</v>
+        <v>0.0097</v>
       </c>
       <c r="G21" s="11" t="n">
-        <v>0.038</v>
+        <v>0.0193</v>
       </c>
       <c r="H21" s="11" t="n">
-        <v>0.076</v>
+        <v>0.0386</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
@@ -13436,13 +13434,13 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>142</v>
+        <v>146.5</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>3.9</v>
+        <v>4.03</v>
       </c>
       <c r="M21" s="9" t="n">
         <v>0.07000000000000001</v>
@@ -13464,7 +13462,7 @@
       </c>
       <c r="Q21" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13478,7 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>0.29</v>
+        <v>0.295</v>
       </c>
       <c r="D22" s="6" t="n">
         <v>1.075</v>
@@ -13489,13 +13487,13 @@
         <v>0.225</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.444</v>
+        <v>0.4322</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>0.8879</v>
+        <v>0.8643999999999999</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>1.7759</v>
+        <v>1.7288</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
@@ -13503,10 +13501,10 @@
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>9.039999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
@@ -13533,7 +13531,7 @@
       </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13600,7 @@
       </c>
       <c r="Q23" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13675,7 @@
       </c>
       <c r="Q24" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -13693,7 +13691,7 @@
         </is>
       </c>
       <c r="C25" s="10" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="D25" s="10" t="n">
         <v>7.52</v>
@@ -13702,13 +13700,13 @@
         <v>2.43</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>0.4238</v>
+        <v>0.4164</v>
       </c>
       <c r="G25" s="11" t="n">
-        <v>0.8476</v>
+        <v>0.8327</v>
       </c>
       <c r="H25" s="11" t="n">
-        <v>1.6952</v>
+        <v>1.6654</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
@@ -13716,13 +13714,13 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>-20.85</v>
+        <v>-21.09</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>175.18</v>
+        <v>177.14</v>
       </c>
       <c r="M25" s="9" t="n">
         <v>4.76</v>
@@ -13744,7 +13742,7 @@
       </c>
       <c r="Q25" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -13819,7 +13817,7 @@
       </c>
       <c r="Q26" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -13888,7 +13886,7 @@
       </c>
       <c r="Q27" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -13963,7 +13961,7 @@
       </c>
       <c r="Q28" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -14038,7 +14036,7 @@
       </c>
       <c r="Q29" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -14060,7 +14058,7 @@
         <v>1.015</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>0.105</v>
+        <v>0.1</v>
       </c>
       <c r="F30" s="11" t="n">
         <v/>
@@ -14080,13 +14078,13 @@
         <v>-1.2</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="L30" s="9" t="n">
         <v>19.54</v>
       </c>
       <c r="M30" s="9" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="N30" s="12" t="inlineStr">
         <is>
@@ -14105,7 +14103,7 @@
       </c>
       <c r="Q30" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -14121,7 +14119,7 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>16.54</v>
+        <v>17.11</v>
       </c>
       <c r="D31" s="6" t="n">
         <v>22.98</v>
@@ -14130,13 +14128,13 @@
         <v>6.4</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>0.1307</v>
+        <v>0.118</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>0.2614</v>
+        <v>0.236</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.472</v>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
@@ -14144,13 +14142,13 @@
         </is>
       </c>
       <c r="J31" s="5" t="n">
-        <v>27.23</v>
+        <v>28.17</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>3.54</v>
+        <v>3.66</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>12.84</v>
+        <v>13.28</v>
       </c>
       <c r="M31" s="5" t="n">
         <v>0.11</v>
@@ -14172,7 +14170,7 @@
       </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -14188,7 +14186,7 @@
         </is>
       </c>
       <c r="C32" s="10" t="n">
-        <v>3.74</v>
+        <v>3.61</v>
       </c>
       <c r="D32" s="10" t="n">
         <v>8.890000000000001</v>
@@ -14197,13 +14195,13 @@
         <v>2.43</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>0.3603</v>
+        <v>0.3823</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.7206</v>
+        <v>0.7645</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>1.4412</v>
+        <v>1.5291</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
@@ -14211,13 +14209,13 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>-24.93</v>
+        <v>-24.07</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>11.51</v>
+        <v>11.11</v>
       </c>
       <c r="L32" s="9" t="n">
-        <v>58.86</v>
+        <v>56.82</v>
       </c>
       <c r="M32" s="9" t="n">
         <v>0.24</v>
@@ -14239,7 +14237,7 @@
       </c>
       <c r="Q32" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14312,7 @@
       </c>
       <c r="Q33" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -14330,7 +14328,7 @@
         </is>
       </c>
       <c r="C34" s="6" t="n">
-        <v>3.83</v>
+        <v>3.9</v>
       </c>
       <c r="D34" s="6" t="n">
         <v>5.16</v>
@@ -14339,13 +14337,13 @@
         <v>2.7</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>0.0692</v>
+        <v>0.0634</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>0.1383</v>
+        <v>0.1269</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>0.2767</v>
+        <v>0.2538</v>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
@@ -14353,13 +14351,13 @@
         </is>
       </c>
       <c r="J34" s="5" t="n">
-        <v>54.71</v>
+        <v>55.71</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>7.01</v>
+        <v>7.13</v>
       </c>
       <c r="M34" s="5" t="n">
         <v>2.02</v>
@@ -14381,7 +14379,7 @@
       </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -14456,7 +14454,7 @@
       </c>
       <c r="Q35" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -14472,22 +14470,22 @@
         </is>
       </c>
       <c r="C36" s="10" t="n">
-        <v>0.205</v>
+        <v>0.215</v>
       </c>
       <c r="D36" s="10" t="n">
         <v>0.325</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>0.082</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>0.25</v>
+        <v>0.2267</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>0.5</v>
+        <v>0.4535</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>1</v>
+        <v>0.907</v>
       </c>
       <c r="I36" s="9" t="inlineStr">
         <is>
@@ -14495,10 +14493,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>-10.25</v>
+        <v>-10.75</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>4.02</v>
+        <v>4.22</v>
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
@@ -14525,7 +14523,7 @@
       </c>
       <c r="Q36" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -14569,11 +14567,13 @@
       <c r="K37" s="9" t="n">
         <v>1.38</v>
       </c>
-      <c r="L37" s="9" t="n">
-        <v>832.01</v>
+      <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
       </c>
       <c r="M37" s="9" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="N37" s="12" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
       </c>
       <c r="Q37" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -14659,7 +14659,7 @@
       </c>
       <c r="Q38" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="Q39" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="Q40" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -14876,7 +14876,7 @@
       </c>
       <c r="Q41" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -14892,7 +14892,7 @@
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
       <c r="D42" s="10" t="n">
         <v>0.019</v>
@@ -14920,7 +14920,7 @@
         </is>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="L42" s="9" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="Q42" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="C43" s="10" t="n">
-        <v>0.12</v>
+        <v>0.125</v>
       </c>
       <c r="D43" s="10" t="n">
         <v>0.31</v>
@@ -14993,7 +14993,7 @@
         </is>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="L43" s="9" t="inlineStr">
         <is>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="Q43" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -15095,7 +15095,7 @@
       </c>
       <c r="Q44" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
@@ -15164,7 +15164,7 @@
       </c>
       <c r="Q45" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01 00:03</t>
+          <t>2026-09-01 22:47</t>
         </is>
       </c>
     </row>
